--- a/tests/eindhoven-500/reference/resultaten/werk/alle groepen/bestemmingen/restdag/Ontpl_totaalproduct_Auto_Fiets.xlsx
+++ b/tests/eindhoven-500/reference/resultaten/werk/alle groepen/bestemmingen/restdag/Ontpl_totaalproduct_Auto_Fiets.xlsx
@@ -388,10 +388,10 @@
         <v>338552</v>
       </c>
       <c r="C2">
-        <v>506815</v>
+        <v>506922</v>
       </c>
       <c r="D2">
-        <v>1001456</v>
+        <v>1001572</v>
       </c>
       <c r="E2">
         <v>1439082</v>
@@ -405,10 +405,10 @@
         <v>143396</v>
       </c>
       <c r="C3">
-        <v>257188</v>
+        <v>257242</v>
       </c>
       <c r="D3">
-        <v>528904</v>
+        <v>528983</v>
       </c>
       <c r="E3">
         <v>662687</v>
@@ -422,13 +422,13 @@
         <v>13679</v>
       </c>
       <c r="C4">
-        <v>22314</v>
+        <v>22315</v>
       </c>
       <c r="D4">
-        <v>49054</v>
+        <v>49059</v>
       </c>
       <c r="E4">
-        <v>69860</v>
+        <v>69871</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -439,13 +439,13 @@
         <v>451419</v>
       </c>
       <c r="C5">
-        <v>691738</v>
+        <v>691780</v>
       </c>
       <c r="D5">
-        <v>1520674</v>
+        <v>1520821</v>
       </c>
       <c r="E5">
-        <v>2305387</v>
+        <v>2305759</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -456,13 +456,13 @@
         <v>725007</v>
       </c>
       <c r="C6">
-        <v>914879</v>
+        <v>914935</v>
       </c>
       <c r="D6">
-        <v>2158376</v>
+        <v>2158584</v>
       </c>
       <c r="E6">
-        <v>4401194</v>
+        <v>4401903</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -473,13 +473,13 @@
         <v>962822</v>
       </c>
       <c r="C7">
-        <v>1146073</v>
+        <v>1147786</v>
       </c>
       <c r="D7">
-        <v>2623419</v>
+        <v>2626100</v>
       </c>
       <c r="E7">
-        <v>5474917</v>
+        <v>5479177</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -490,13 +490,13 @@
         <v>3295293</v>
       </c>
       <c r="C8">
-        <v>4788947</v>
+        <v>4796107</v>
       </c>
       <c r="D8">
-        <v>8448298</v>
+        <v>8456933</v>
       </c>
       <c r="E8">
-        <v>8244580</v>
+        <v>8250996</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -507,13 +507,13 @@
         <v>1687745</v>
       </c>
       <c r="C9">
-        <v>2639020</v>
+        <v>2647456</v>
       </c>
       <c r="D9">
-        <v>4187433</v>
+        <v>4201833</v>
       </c>
       <c r="E9">
-        <v>2745421</v>
+        <v>2753018</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -524,13 +524,13 @@
         <v>1220479</v>
       </c>
       <c r="C10">
-        <v>2680992</v>
+        <v>2685000</v>
       </c>
       <c r="D10">
-        <v>4090755</v>
+        <v>4094936</v>
       </c>
       <c r="E10">
-        <v>1739091</v>
+        <v>1740445</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -541,13 +541,13 @@
         <v>1084870</v>
       </c>
       <c r="C11">
-        <v>1800972</v>
+        <v>1803664</v>
       </c>
       <c r="D11">
-        <v>2845742</v>
+        <v>2848651</v>
       </c>
       <c r="E11">
-        <v>1867913</v>
+        <v>1869366</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -558,10 +558,10 @@
         <v>396306</v>
       </c>
       <c r="C12">
-        <v>464263</v>
+        <v>464315</v>
       </c>
       <c r="D12">
-        <v>1177904</v>
+        <v>1178050</v>
       </c>
       <c r="E12">
         <v>3161801</v>
@@ -575,10 +575,10 @@
         <v>1609225</v>
       </c>
       <c r="C13">
-        <v>3034814</v>
+        <v>3035451</v>
       </c>
       <c r="D13">
-        <v>6717085</v>
+        <v>6718080</v>
       </c>
       <c r="E13">
         <v>9277620</v>
@@ -592,10 +592,10 @@
         <v>473011</v>
       </c>
       <c r="C14">
-        <v>1076245</v>
+        <v>1076366</v>
       </c>
       <c r="D14">
-        <v>3109667</v>
+        <v>3110052</v>
       </c>
       <c r="E14">
         <v>5842458</v>
@@ -609,13 +609,13 @@
         <v>1600183</v>
       </c>
       <c r="C15">
-        <v>2292146</v>
+        <v>2295572</v>
       </c>
       <c r="D15">
-        <v>5024514</v>
+        <v>5029649</v>
       </c>
       <c r="E15">
-        <v>7729294</v>
+        <v>7735309</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -626,13 +626,13 @@
         <v>3339296</v>
       </c>
       <c r="C16">
-        <v>5124623</v>
+        <v>5128959</v>
       </c>
       <c r="D16">
-        <v>9876028</v>
+        <v>9885376</v>
       </c>
       <c r="E16">
-        <v>10912538</v>
+        <v>10919426</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -643,10 +643,10 @@
         <v>958805</v>
       </c>
       <c r="C17">
-        <v>1624919</v>
+        <v>1625102</v>
       </c>
       <c r="D17">
-        <v>3392364</v>
+        <v>3392784</v>
       </c>
       <c r="E17">
         <v>4330292</v>
@@ -660,10 +660,10 @@
         <v>1003774</v>
       </c>
       <c r="C18">
-        <v>1646001</v>
+        <v>1646346</v>
       </c>
       <c r="D18">
-        <v>3861002</v>
+        <v>3861573</v>
       </c>
       <c r="E18">
         <v>6995031</v>
@@ -677,13 +677,13 @@
         <v>2065267</v>
       </c>
       <c r="C19">
-        <v>3097299</v>
+        <v>3099920</v>
       </c>
       <c r="D19">
-        <v>6477395</v>
+        <v>6483526</v>
       </c>
       <c r="E19">
-        <v>8671044</v>
+        <v>8676517</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -694,13 +694,13 @@
         <v>1622710</v>
       </c>
       <c r="C20">
-        <v>2365210</v>
+        <v>2367212</v>
       </c>
       <c r="D20">
-        <v>5117942</v>
+        <v>5122786</v>
       </c>
       <c r="E20">
-        <v>7550297</v>
+        <v>7555062</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -711,13 +711,13 @@
         <v>1823873</v>
       </c>
       <c r="C21">
-        <v>2552926</v>
+        <v>2555086</v>
       </c>
       <c r="D21">
-        <v>4118344</v>
+        <v>4122242</v>
       </c>
       <c r="E21">
-        <v>3362241</v>
+        <v>3364364</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -728,13 +728,13 @@
         <v>872585</v>
       </c>
       <c r="C22">
-        <v>1203660</v>
+        <v>1203880</v>
       </c>
       <c r="D22">
-        <v>2542460</v>
+        <v>2542855</v>
       </c>
       <c r="E22">
-        <v>4993909</v>
+        <v>4995134</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -745,10 +745,10 @@
         <v>200054</v>
       </c>
       <c r="C23">
-        <v>460741</v>
+        <v>460838</v>
       </c>
       <c r="D23">
-        <v>953767</v>
+        <v>953878</v>
       </c>
       <c r="E23">
         <v>959388</v>
@@ -762,13 +762,13 @@
         <v>2357015</v>
       </c>
       <c r="C24">
-        <v>4103850</v>
+        <v>4103955</v>
       </c>
       <c r="D24">
-        <v>8635100</v>
+        <v>8635523</v>
       </c>
       <c r="E24">
-        <v>9973171</v>
+        <v>9974210</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -779,13 +779,13 @@
         <v>1535304</v>
       </c>
       <c r="C25">
-        <v>2496509</v>
+        <v>2496573</v>
       </c>
       <c r="D25">
-        <v>5730566</v>
+        <v>5730847</v>
       </c>
       <c r="E25">
-        <v>8489068</v>
+        <v>8489953</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -796,13 +796,13 @@
         <v>10812</v>
       </c>
       <c r="C26">
-        <v>17099</v>
+        <v>17100</v>
       </c>
       <c r="D26">
-        <v>39250</v>
+        <v>39252</v>
       </c>
       <c r="E26">
-        <v>59364</v>
+        <v>59370</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -813,13 +813,13 @@
         <v>1263554</v>
       </c>
       <c r="C27">
-        <v>2086197</v>
+        <v>2086198</v>
       </c>
       <c r="D27">
-        <v>4476730</v>
+        <v>4477084</v>
       </c>
       <c r="E27">
-        <v>6181961</v>
+        <v>6182885</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -830,13 +830,13 @@
         <v>858569</v>
       </c>
       <c r="C28">
-        <v>1448066</v>
+        <v>1448067</v>
       </c>
       <c r="D28">
-        <v>2950572</v>
+        <v>2950805</v>
       </c>
       <c r="E28">
-        <v>3410737</v>
+        <v>3411247</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -847,13 +847,13 @@
         <v>518381</v>
       </c>
       <c r="C29">
-        <v>908109</v>
+        <v>908110</v>
       </c>
       <c r="D29">
-        <v>1271798</v>
+        <v>1271899</v>
       </c>
       <c r="E29">
-        <v>568456</v>
+        <v>568541</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -864,13 +864,13 @@
         <v>4599127</v>
       </c>
       <c r="C30">
-        <v>7255764</v>
+        <v>7282388</v>
       </c>
       <c r="D30">
-        <v>8805400</v>
+        <v>8857940</v>
       </c>
       <c r="E30">
-        <v>5782026</v>
+        <v>5799863</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -881,13 +881,13 @@
         <v>7254576</v>
       </c>
       <c r="C31">
-        <v>11701697</v>
+        <v>11744635</v>
       </c>
       <c r="D31">
-        <v>15017799</v>
+        <v>15107408</v>
       </c>
       <c r="E31">
-        <v>10944549</v>
+        <v>10978311</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -898,13 +898,13 @@
         <v>4622612</v>
       </c>
       <c r="C32">
-        <v>5720662</v>
+        <v>5730192</v>
       </c>
       <c r="D32">
-        <v>10181369</v>
+        <v>10202015</v>
       </c>
       <c r="E32">
-        <v>19723065</v>
+        <v>19739362</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -915,13 +915,13 @@
         <v>6214297</v>
       </c>
       <c r="C33">
-        <v>8607328</v>
+        <v>8638911</v>
       </c>
       <c r="D33">
-        <v>13289131</v>
+        <v>13368425</v>
       </c>
       <c r="E33">
-        <v>16313572</v>
+        <v>16363898</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -929,16 +929,16 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>605707</v>
+        <v>605867</v>
       </c>
       <c r="C34">
-        <v>512826</v>
+        <v>513005</v>
       </c>
       <c r="D34">
-        <v>989872</v>
+        <v>990087</v>
       </c>
       <c r="E34">
-        <v>4265742</v>
+        <v>4266315</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -949,10 +949,10 @@
         <v>2484966</v>
       </c>
       <c r="C35">
-        <v>3172637</v>
+        <v>3173217</v>
       </c>
       <c r="D35">
-        <v>5062521</v>
+        <v>5064226</v>
       </c>
       <c r="E35">
         <v>8139793</v>
@@ -966,13 +966,13 @@
         <v>10711499</v>
       </c>
       <c r="C36">
-        <v>16978782</v>
+        <v>16982708</v>
       </c>
       <c r="D36">
-        <v>30119855</v>
+        <v>30169890</v>
       </c>
       <c r="E36">
-        <v>40528392</v>
+        <v>40567024</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -983,13 +983,13 @@
         <v>16018183</v>
       </c>
       <c r="C37">
-        <v>24975444</v>
+        <v>24996311</v>
       </c>
       <c r="D37">
-        <v>30751331</v>
+        <v>30913958</v>
       </c>
       <c r="E37">
-        <v>21235853</v>
+        <v>21297586</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -1000,13 +1000,13 @@
         <v>16948817</v>
       </c>
       <c r="C38">
-        <v>21111049</v>
+        <v>21128687</v>
       </c>
       <c r="D38">
-        <v>29681719</v>
+        <v>29838689</v>
       </c>
       <c r="E38">
-        <v>34031816</v>
+        <v>34130747</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -1014,16 +1014,16 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>816525</v>
+        <v>817053</v>
       </c>
       <c r="C39">
-        <v>1696943</v>
+        <v>1700373</v>
       </c>
       <c r="D39">
-        <v>1647442</v>
+        <v>1650041</v>
       </c>
       <c r="E39">
-        <v>539167</v>
+        <v>539515</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -1034,13 +1034,13 @@
         <v>123458</v>
       </c>
       <c r="C40">
-        <v>156131</v>
+        <v>156147</v>
       </c>
       <c r="D40">
-        <v>213935</v>
+        <v>213984</v>
       </c>
       <c r="E40">
-        <v>251870</v>
+        <v>251901</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -1051,10 +1051,10 @@
         <v>39444</v>
       </c>
       <c r="C41">
-        <v>50359</v>
+        <v>50369</v>
       </c>
       <c r="D41">
-        <v>69350</v>
+        <v>69373</v>
       </c>
       <c r="E41">
         <v>83059</v>
@@ -1068,13 +1068,13 @@
         <v>13076169</v>
       </c>
       <c r="C42">
-        <v>13882469</v>
+        <v>13885751</v>
       </c>
       <c r="D42">
-        <v>25823702</v>
+        <v>25870211</v>
       </c>
       <c r="E42">
-        <v>61077583</v>
+        <v>61130535</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -1085,10 +1085,10 @@
         <v>15422850</v>
       </c>
       <c r="C43">
-        <v>15545097</v>
+        <v>15546639</v>
       </c>
       <c r="D43">
-        <v>28379131</v>
+        <v>28389668</v>
       </c>
       <c r="E43">
         <v>74440808</v>
@@ -1102,13 +1102,13 @@
         <v>6260388</v>
       </c>
       <c r="C44">
-        <v>7359878</v>
+        <v>7361535</v>
       </c>
       <c r="D44">
-        <v>11040029</v>
+        <v>11043238</v>
       </c>
       <c r="E44">
-        <v>16328700</v>
+        <v>16332587</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -1119,13 +1119,13 @@
         <v>3288765</v>
       </c>
       <c r="C45">
-        <v>5665867</v>
+        <v>5666544</v>
       </c>
       <c r="D45">
-        <v>10858115</v>
+        <v>10875245</v>
       </c>
       <c r="E45">
-        <v>15749896</v>
+        <v>15763629</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -1136,13 +1136,13 @@
         <v>5739744</v>
       </c>
       <c r="C46">
-        <v>8154832</v>
+        <v>8158600</v>
       </c>
       <c r="D46">
-        <v>12845161</v>
+        <v>12869141</v>
       </c>
       <c r="E46">
-        <v>16512756</v>
+        <v>16525717</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -1153,13 +1153,13 @@
         <v>1380154</v>
       </c>
       <c r="C47">
-        <v>2280748</v>
+        <v>2280869</v>
       </c>
       <c r="D47">
-        <v>5071251</v>
+        <v>5072441</v>
       </c>
       <c r="E47">
-        <v>13528163</v>
+        <v>13531452</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -1170,10 +1170,10 @@
         <v>1433383</v>
       </c>
       <c r="C48">
-        <v>1844522</v>
+        <v>1844608</v>
       </c>
       <c r="D48">
-        <v>3321666</v>
+        <v>3322685</v>
       </c>
       <c r="E48">
         <v>6242030</v>
@@ -1187,13 +1187,13 @@
         <v>12097447</v>
       </c>
       <c r="C49">
-        <v>16738440</v>
+        <v>16768081</v>
       </c>
       <c r="D49">
-        <v>28616269</v>
+        <v>28644316</v>
       </c>
       <c r="E49">
-        <v>30105396</v>
+        <v>30122060</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -1204,10 +1204,10 @@
         <v>5932343</v>
       </c>
       <c r="C50">
-        <v>8159979</v>
+        <v>8159983</v>
       </c>
       <c r="D50">
-        <v>15127789</v>
+        <v>15129456</v>
       </c>
       <c r="E50">
         <v>18889237</v>
@@ -1221,10 +1221,10 @@
         <v>3496265</v>
       </c>
       <c r="C51">
-        <v>5262013</v>
+        <v>5263019</v>
       </c>
       <c r="D51">
-        <v>9790764</v>
+        <v>9792003</v>
       </c>
       <c r="E51">
         <v>11566481</v>
@@ -1238,10 +1238,10 @@
         <v>1774318</v>
       </c>
       <c r="C52">
-        <v>2385408</v>
+        <v>2386217</v>
       </c>
       <c r="D52">
-        <v>5311543</v>
+        <v>5312223</v>
       </c>
       <c r="E52">
         <v>10224293</v>
@@ -1255,13 +1255,13 @@
         <v>7303813</v>
       </c>
       <c r="C53">
-        <v>10969526</v>
+        <v>10977086</v>
       </c>
       <c r="D53">
-        <v>18524486</v>
+        <v>18542536</v>
       </c>
       <c r="E53">
-        <v>16607979</v>
+        <v>16616345</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -1272,13 +1272,13 @@
         <v>7520551</v>
       </c>
       <c r="C54">
-        <v>12024426</v>
+        <v>12032198</v>
       </c>
       <c r="D54">
-        <v>25024052</v>
+        <v>25048418</v>
       </c>
       <c r="E54">
-        <v>32151477</v>
+        <v>32167892</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -1289,10 +1289,10 @@
         <v>1303318</v>
       </c>
       <c r="C55">
-        <v>2439793</v>
+        <v>2439794</v>
       </c>
       <c r="D55">
-        <v>5399838</v>
+        <v>5400432</v>
       </c>
       <c r="E55">
         <v>7152235</v>
@@ -1306,10 +1306,10 @@
         <v>1060719</v>
       </c>
       <c r="C56">
-        <v>1336344</v>
+        <v>1336870</v>
       </c>
       <c r="D56">
-        <v>2914762</v>
+        <v>2915101</v>
       </c>
       <c r="E56">
         <v>6220301</v>
@@ -1323,13 +1323,13 @@
         <v>6160716</v>
       </c>
       <c r="C57">
-        <v>9020169</v>
+        <v>9020950</v>
       </c>
       <c r="D57">
-        <v>20392049</v>
+        <v>20393605</v>
       </c>
       <c r="E57">
-        <v>34872275</v>
+        <v>34875817</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -1340,13 +1340,13 @@
         <v>2591771</v>
       </c>
       <c r="C58">
-        <v>3882453</v>
+        <v>3882462</v>
       </c>
       <c r="D58">
-        <v>8483818</v>
+        <v>8484215</v>
       </c>
       <c r="E58">
-        <v>13120406</v>
+        <v>13121889</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -1357,13 +1357,13 @@
         <v>562687</v>
       </c>
       <c r="C59">
-        <v>757552</v>
+        <v>757554</v>
       </c>
       <c r="D59">
-        <v>1677591</v>
+        <v>1677670</v>
       </c>
       <c r="E59">
-        <v>2938424</v>
+        <v>2938756</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -1374,13 +1374,13 @@
         <v>3551635</v>
       </c>
       <c r="C60">
-        <v>6280335</v>
+        <v>6280336</v>
       </c>
       <c r="D60">
-        <v>13167765</v>
+        <v>13168277</v>
       </c>
       <c r="E60">
-        <v>13992590</v>
+        <v>13993862</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -1391,13 +1391,13 @@
         <v>1087235</v>
       </c>
       <c r="C61">
-        <v>1783110</v>
+        <v>1783111</v>
       </c>
       <c r="D61">
-        <v>4463024</v>
+        <v>4463197</v>
       </c>
       <c r="E61">
-        <v>7251221</v>
+        <v>7251880</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -1408,13 +1408,13 @@
         <v>1165775</v>
       </c>
       <c r="C62">
-        <v>2401292</v>
+        <v>2401296</v>
       </c>
       <c r="D62">
-        <v>6557725</v>
+        <v>6557950</v>
       </c>
       <c r="E62">
-        <v>8517831</v>
+        <v>8518398</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -1425,13 +1425,13 @@
         <v>436448</v>
       </c>
       <c r="C63">
-        <v>851367</v>
+        <v>851369</v>
       </c>
       <c r="D63">
-        <v>2539511</v>
+        <v>2539598</v>
       </c>
       <c r="E63">
-        <v>4179557</v>
+        <v>4179835</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -1442,13 +1442,13 @@
         <v>420321</v>
       </c>
       <c r="C64">
-        <v>951526</v>
+        <v>951550</v>
       </c>
       <c r="D64">
-        <v>3080653</v>
+        <v>3080757</v>
       </c>
       <c r="E64">
-        <v>5049088</v>
+        <v>5049397</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -1459,13 +1459,13 @@
         <v>132733</v>
       </c>
       <c r="C65">
-        <v>209336</v>
+        <v>209341</v>
       </c>
       <c r="D65">
-        <v>724859</v>
+        <v>724884</v>
       </c>
       <c r="E65">
-        <v>2019635</v>
+        <v>2019759</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -1476,13 +1476,13 @@
         <v>6577342</v>
       </c>
       <c r="C66">
-        <v>11132909</v>
+        <v>11146342</v>
       </c>
       <c r="D66">
-        <v>20493054</v>
+        <v>20530933</v>
       </c>
       <c r="E66">
-        <v>25721208</v>
+        <v>25750627</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -1493,10 +1493,10 @@
         <v>1876930</v>
       </c>
       <c r="C67">
-        <v>2357768</v>
+        <v>2358237</v>
       </c>
       <c r="D67">
-        <v>5246679</v>
+        <v>5248498</v>
       </c>
       <c r="E67">
         <v>15295101</v>
@@ -1510,13 +1510,13 @@
         <v>4695541</v>
       </c>
       <c r="C68">
-        <v>8871537</v>
+        <v>8882241</v>
       </c>
       <c r="D68">
-        <v>14850810</v>
+        <v>14878261</v>
       </c>
       <c r="E68">
-        <v>13871329</v>
+        <v>13887194</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -1527,10 +1527,10 @@
         <v>5056670</v>
       </c>
       <c r="C69">
-        <v>8959519</v>
+        <v>8961302</v>
       </c>
       <c r="D69">
-        <v>15496005</v>
+        <v>15501379</v>
       </c>
       <c r="E69">
         <v>19311996</v>
@@ -1544,10 +1544,10 @@
         <v>2627702</v>
       </c>
       <c r="C70">
-        <v>4316530</v>
+        <v>4317389</v>
       </c>
       <c r="D70">
-        <v>7748002</v>
+        <v>7750690</v>
       </c>
       <c r="E70">
         <v>11278206</v>
@@ -1561,13 +1561,13 @@
         <v>316537</v>
       </c>
       <c r="C71">
-        <v>538436</v>
+        <v>538505</v>
       </c>
       <c r="D71">
-        <v>855580</v>
+        <v>855862</v>
       </c>
       <c r="E71">
-        <v>1123810</v>
+        <v>1124134</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -1578,13 +1578,13 @@
         <v>571931</v>
       </c>
       <c r="C72">
-        <v>842911</v>
+        <v>843004</v>
       </c>
       <c r="D72">
-        <v>1326148</v>
+        <v>1326549</v>
       </c>
       <c r="E72">
-        <v>1642878</v>
+        <v>1643355</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -1595,13 +1595,13 @@
         <v>1096201</v>
       </c>
       <c r="C73">
-        <v>1762450</v>
+        <v>1762644</v>
       </c>
       <c r="D73">
-        <v>3283795</v>
+        <v>3284789</v>
       </c>
       <c r="E73">
-        <v>5319796</v>
+        <v>5321341</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -1612,13 +1612,13 @@
         <v>428948</v>
       </c>
       <c r="C74">
-        <v>651340</v>
+        <v>651412</v>
       </c>
       <c r="D74">
-        <v>1199848</v>
+        <v>1200211</v>
       </c>
       <c r="E74">
-        <v>1799343</v>
+        <v>1799865</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -1629,13 +1629,13 @@
         <v>875273</v>
       </c>
       <c r="C75">
-        <v>1264012</v>
+        <v>1264035</v>
       </c>
       <c r="D75">
-        <v>2665213</v>
+        <v>2665490</v>
       </c>
       <c r="E75">
-        <v>4935577</v>
+        <v>4936732</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -1646,10 +1646,10 @@
         <v>2605621</v>
       </c>
       <c r="C76">
-        <v>5187090</v>
+        <v>5188122</v>
       </c>
       <c r="D76">
-        <v>10188318</v>
+        <v>10191852</v>
       </c>
       <c r="E76">
         <v>14677117</v>
@@ -1663,13 +1663,13 @@
         <v>4535904</v>
       </c>
       <c r="C77">
-        <v>7805136</v>
+        <v>7805537</v>
       </c>
       <c r="D77">
-        <v>13856858</v>
+        <v>13860166</v>
       </c>
       <c r="E77">
-        <v>17990557</v>
+        <v>17995715</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -1680,13 +1680,13 @@
         <v>902777</v>
       </c>
       <c r="C78">
-        <v>1481530</v>
+        <v>1481607</v>
       </c>
       <c r="D78">
-        <v>2648200</v>
+        <v>2648832</v>
       </c>
       <c r="E78">
-        <v>3551784</v>
+        <v>3552802</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -1697,13 +1697,13 @@
         <v>110095</v>
       </c>
       <c r="C79">
-        <v>180674</v>
+        <v>180684</v>
       </c>
       <c r="D79">
-        <v>369516</v>
+        <v>369604</v>
       </c>
       <c r="E79">
-        <v>463276</v>
+        <v>463409</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -1714,13 +1714,13 @@
         <v>660569</v>
       </c>
       <c r="C80">
-        <v>794968</v>
+        <v>795008</v>
       </c>
       <c r="D80">
-        <v>1354893</v>
+        <v>1355216</v>
       </c>
       <c r="E80">
-        <v>2548019</v>
+        <v>2548749</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -1731,13 +1731,13 @@
         <v>5410610</v>
       </c>
       <c r="C81">
-        <v>8057447</v>
+        <v>8059483</v>
       </c>
       <c r="D81">
-        <v>13239771</v>
+        <v>13243035</v>
       </c>
       <c r="E81">
-        <v>18511774</v>
+        <v>18516357</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -1748,13 +1748,13 @@
         <v>640309</v>
       </c>
       <c r="C82">
-        <v>760981</v>
+        <v>761173</v>
       </c>
       <c r="D82">
-        <v>1257778</v>
+        <v>1258088</v>
       </c>
       <c r="E82">
-        <v>2154388</v>
+        <v>2154921</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -1765,13 +1765,13 @@
         <v>5211075</v>
       </c>
       <c r="C83">
-        <v>8004207</v>
+        <v>8004222</v>
       </c>
       <c r="D83">
-        <v>13976467</v>
+        <v>13977882</v>
       </c>
       <c r="E83">
-        <v>19082355</v>
+        <v>19087171</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -1782,13 +1782,13 @@
         <v>1178156</v>
       </c>
       <c r="C84">
-        <v>1677738</v>
+        <v>1677741</v>
       </c>
       <c r="D84">
-        <v>3261176</v>
+        <v>3261506</v>
       </c>
       <c r="E84">
-        <v>6045173</v>
+        <v>6046699</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -1799,13 +1799,13 @@
         <v>6153760</v>
       </c>
       <c r="C85">
-        <v>9590147</v>
+        <v>9590332</v>
       </c>
       <c r="D85">
-        <v>14217298</v>
+        <v>14220663</v>
       </c>
       <c r="E85">
-        <v>16041442</v>
+        <v>16045080</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -1816,13 +1816,13 @@
         <v>3166847</v>
       </c>
       <c r="C86">
-        <v>4020112</v>
+        <v>4020190</v>
       </c>
       <c r="D86">
-        <v>5986231</v>
+        <v>5987648</v>
       </c>
       <c r="E86">
-        <v>8582172</v>
+        <v>8584118</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -1833,13 +1833,13 @@
         <v>3508395</v>
       </c>
       <c r="C87">
-        <v>5822240</v>
+        <v>5823519</v>
       </c>
       <c r="D87">
-        <v>9835382</v>
+        <v>9838159</v>
       </c>
       <c r="E87">
-        <v>14040338</v>
+        <v>14043638</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -1850,13 +1850,13 @@
         <v>756713</v>
       </c>
       <c r="C88">
-        <v>721765</v>
+        <v>721924</v>
       </c>
       <c r="D88">
-        <v>1375578</v>
+        <v>1375966</v>
       </c>
       <c r="E88">
-        <v>4788323</v>
+        <v>4789449</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -1867,13 +1867,13 @@
         <v>1582217</v>
       </c>
       <c r="C89">
-        <v>1780354</v>
+        <v>1780746</v>
       </c>
       <c r="D89">
-        <v>2613598</v>
+        <v>2614336</v>
       </c>
       <c r="E89">
-        <v>3895585</v>
+        <v>3896501</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -1881,16 +1881,16 @@
         <v>89</v>
       </c>
       <c r="B90">
-        <v>27219431</v>
+        <v>27220166</v>
       </c>
       <c r="C90">
-        <v>29311455</v>
+        <v>29509455</v>
       </c>
       <c r="D90">
-        <v>40398053</v>
+        <v>41542936</v>
       </c>
       <c r="E90">
-        <v>61448976</v>
+        <v>63243802</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -1898,16 +1898,16 @@
         <v>90</v>
       </c>
       <c r="B91">
-        <v>16147440</v>
+        <v>16147883</v>
       </c>
       <c r="C91">
-        <v>18134996</v>
+        <v>18262405</v>
       </c>
       <c r="D91">
-        <v>28210581</v>
+        <v>29066777</v>
       </c>
       <c r="E91">
-        <v>53701915</v>
+        <v>55451555</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -1915,16 +1915,16 @@
         <v>91</v>
       </c>
       <c r="B92">
-        <v>12900371</v>
+        <v>12900749</v>
       </c>
       <c r="C92">
-        <v>14008739</v>
+        <v>14123662</v>
       </c>
       <c r="D92">
-        <v>22489028</v>
+        <v>23372116</v>
       </c>
       <c r="E92">
-        <v>48631254</v>
+        <v>50953776</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -1932,16 +1932,16 @@
         <v>92</v>
       </c>
       <c r="B93">
-        <v>1073581</v>
+        <v>1073606</v>
       </c>
       <c r="C93">
-        <v>1550117</v>
+        <v>1557445</v>
       </c>
       <c r="D93">
-        <v>2303818</v>
+        <v>2335384</v>
       </c>
       <c r="E93">
-        <v>2979656</v>
+        <v>2995082</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -1949,16 +1949,16 @@
         <v>93</v>
       </c>
       <c r="B94">
-        <v>6244332</v>
+        <v>6245391</v>
       </c>
       <c r="C94">
-        <v>7431930</v>
+        <v>7474815</v>
       </c>
       <c r="D94">
-        <v>5482425</v>
+        <v>5709507</v>
       </c>
       <c r="E94">
-        <v>2091416</v>
+        <v>2220613</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -1966,16 +1966,16 @@
         <v>94</v>
       </c>
       <c r="B95">
-        <v>14260107</v>
+        <v>14260448</v>
       </c>
       <c r="C95">
-        <v>15926927</v>
+        <v>16005089</v>
       </c>
       <c r="D95">
-        <v>25092108</v>
+        <v>25467850</v>
       </c>
       <c r="E95">
-        <v>48853625</v>
+        <v>49206861</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -1983,16 +1983,16 @@
         <v>95</v>
       </c>
       <c r="B96">
-        <v>12298996</v>
+        <v>12299349</v>
       </c>
       <c r="C96">
-        <v>13487868</v>
+        <v>13593073</v>
       </c>
       <c r="D96">
-        <v>17439669</v>
+        <v>18070663</v>
       </c>
       <c r="E96">
-        <v>22915655</v>
+        <v>23888766</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -2000,16 +2000,16 @@
         <v>96</v>
       </c>
       <c r="B97">
-        <v>5099508</v>
+        <v>5099629</v>
       </c>
       <c r="C97">
-        <v>4133647</v>
+        <v>4153187</v>
       </c>
       <c r="D97">
-        <v>7174747</v>
+        <v>7273055</v>
       </c>
       <c r="E97">
-        <v>24464545</v>
+        <v>24591204</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -2017,16 +2017,16 @@
         <v>97</v>
       </c>
       <c r="B98">
-        <v>14386964</v>
+        <v>14387755</v>
       </c>
       <c r="C98">
-        <v>15247170</v>
+        <v>15349185</v>
       </c>
       <c r="D98">
-        <v>23635092</v>
+        <v>24035804</v>
       </c>
       <c r="E98">
-        <v>44940322</v>
+        <v>45229600</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -2034,16 +2034,16 @@
         <v>98</v>
       </c>
       <c r="B99">
-        <v>7747924</v>
+        <v>7748375</v>
       </c>
       <c r="C99">
-        <v>9196022</v>
+        <v>9268442</v>
       </c>
       <c r="D99">
-        <v>12902348</v>
+        <v>13214586</v>
       </c>
       <c r="E99">
-        <v>17971561</v>
+        <v>18284874</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -2054,13 +2054,13 @@
         <v>8829833</v>
       </c>
       <c r="C100">
-        <v>10527153</v>
+        <v>10560001</v>
       </c>
       <c r="D100">
-        <v>12593305</v>
+        <v>12781287</v>
       </c>
       <c r="E100">
-        <v>12819838</v>
+        <v>12962304</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -2071,13 +2071,13 @@
         <v>3579046</v>
       </c>
       <c r="C101">
-        <v>4360994</v>
+        <v>4376095</v>
       </c>
       <c r="D101">
-        <v>6610191</v>
+        <v>6732468</v>
       </c>
       <c r="E101">
-        <v>10633941</v>
+        <v>10823860</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -2088,13 +2088,13 @@
         <v>1488270</v>
       </c>
       <c r="C102">
-        <v>803252</v>
+        <v>805506</v>
       </c>
       <c r="D102">
-        <v>1346962</v>
+        <v>1362719</v>
       </c>
       <c r="E102">
-        <v>6533558</v>
+        <v>6566778</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -2102,16 +2102,16 @@
         <v>102</v>
       </c>
       <c r="B103">
-        <v>13784914</v>
+        <v>13784950</v>
       </c>
       <c r="C103">
-        <v>16729504</v>
+        <v>16850641</v>
       </c>
       <c r="D103">
-        <v>18537054</v>
+        <v>18862320</v>
       </c>
       <c r="E103">
-        <v>15059573</v>
+        <v>15158835</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -2119,16 +2119,16 @@
         <v>103</v>
       </c>
       <c r="B104">
-        <v>17995868</v>
+        <v>17995915</v>
       </c>
       <c r="C104">
-        <v>18956945</v>
+        <v>19094211</v>
       </c>
       <c r="D104">
-        <v>29039275</v>
+        <v>29548822</v>
       </c>
       <c r="E104">
-        <v>53364947</v>
+        <v>53716694</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -2139,13 +2139,13 @@
         <v>5586823</v>
       </c>
       <c r="C105">
-        <v>5793293</v>
+        <v>5800800</v>
       </c>
       <c r="D105">
-        <v>8674984</v>
+        <v>8704181</v>
       </c>
       <c r="E105">
-        <v>15769750</v>
+        <v>15801489</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -2153,16 +2153,16 @@
         <v>105</v>
       </c>
       <c r="B106">
-        <v>3266737</v>
+        <v>3266740</v>
       </c>
       <c r="C106">
-        <v>1875416</v>
+        <v>1878628</v>
       </c>
       <c r="D106">
-        <v>3436508</v>
+        <v>3440979</v>
       </c>
       <c r="E106">
-        <v>17525816</v>
+        <v>17535177</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -2170,16 +2170,16 @@
         <v>106</v>
       </c>
       <c r="B107">
-        <v>8026839</v>
+        <v>8026847</v>
       </c>
       <c r="C107">
-        <v>6505350</v>
+        <v>6516489</v>
       </c>
       <c r="D107">
-        <v>11149559</v>
+        <v>11164065</v>
       </c>
       <c r="E107">
-        <v>36179531</v>
+        <v>36198855</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -2190,10 +2190,10 @@
         <v>50653</v>
       </c>
       <c r="C108">
-        <v>63832</v>
+        <v>63837</v>
       </c>
       <c r="D108">
-        <v>80479</v>
+        <v>80490</v>
       </c>
       <c r="E108">
         <v>181051</v>
@@ -2204,16 +2204,16 @@
         <v>108</v>
       </c>
       <c r="B109">
-        <v>5252642</v>
+        <v>5252967</v>
       </c>
       <c r="C109">
-        <v>6441563</v>
+        <v>6466558</v>
       </c>
       <c r="D109">
-        <v>11678405</v>
+        <v>11727058</v>
       </c>
       <c r="E109">
-        <v>27649875</v>
+        <v>27708269</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -2221,16 +2221,16 @@
         <v>109</v>
       </c>
       <c r="B110">
-        <v>40718</v>
+        <v>40721</v>
       </c>
       <c r="C110">
-        <v>51124</v>
+        <v>51322</v>
       </c>
       <c r="D110">
-        <v>68696</v>
+        <v>68983</v>
       </c>
       <c r="E110">
-        <v>81085</v>
+        <v>81256</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -2238,16 +2238,16 @@
         <v>110</v>
       </c>
       <c r="B111">
-        <v>20685980</v>
+        <v>20687360</v>
       </c>
       <c r="C111">
-        <v>27510618</v>
+        <v>27642132</v>
       </c>
       <c r="D111">
-        <v>31931314</v>
+        <v>32170644</v>
       </c>
       <c r="E111">
-        <v>26643763</v>
+        <v>26840462</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -2255,16 +2255,16 @@
         <v>111</v>
       </c>
       <c r="B112">
-        <v>10237255</v>
+        <v>10240417</v>
       </c>
       <c r="C112">
-        <v>12593226</v>
+        <v>12734356</v>
       </c>
       <c r="D112">
-        <v>17586358</v>
+        <v>17922561</v>
       </c>
       <c r="E112">
-        <v>22759471</v>
+        <v>22906572</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -2275,13 +2275,13 @@
         <v>13342504</v>
       </c>
       <c r="C113">
-        <v>16381854</v>
+        <v>16435806</v>
       </c>
       <c r="D113">
-        <v>13950082</v>
+        <v>14009305</v>
       </c>
       <c r="E113">
-        <v>5058869</v>
+        <v>5071439</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -2292,13 +2292,13 @@
         <v>9073287</v>
       </c>
       <c r="C114">
-        <v>9467689</v>
+        <v>9481458</v>
       </c>
       <c r="D114">
-        <v>16052161</v>
+        <v>16073169</v>
       </c>
       <c r="E114">
-        <v>37502322</v>
+        <v>37523595</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -2306,16 +2306,16 @@
         <v>114</v>
       </c>
       <c r="B115">
-        <v>7529104</v>
+        <v>7531465</v>
       </c>
       <c r="C115">
-        <v>9643704</v>
+        <v>9756524</v>
       </c>
       <c r="D115">
-        <v>10503771</v>
+        <v>10725722</v>
       </c>
       <c r="E115">
-        <v>7856118</v>
+        <v>7929418</v>
       </c>
     </row>
     <row r="116" spans="1:5">
@@ -2323,16 +2323,16 @@
         <v>115</v>
       </c>
       <c r="B116">
-        <v>19085735</v>
+        <v>19091631</v>
       </c>
       <c r="C116">
-        <v>22419759</v>
+        <v>22671013</v>
       </c>
       <c r="D116">
-        <v>30202658</v>
+        <v>30780051</v>
       </c>
       <c r="E116">
-        <v>38372623</v>
+        <v>38620637</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -2343,13 +2343,13 @@
         <v>2542501</v>
       </c>
       <c r="C117">
-        <v>2599529</v>
+        <v>2607979</v>
       </c>
       <c r="D117">
-        <v>4272721</v>
+        <v>4290076</v>
       </c>
       <c r="E117">
-        <v>9408999</v>
+        <v>9429487</v>
       </c>
     </row>
     <row r="118" spans="1:5">
@@ -2360,13 +2360,13 @@
         <v>50596</v>
       </c>
       <c r="C118">
-        <v>63878</v>
+        <v>63889</v>
       </c>
       <c r="D118">
-        <v>81212</v>
+        <v>81221</v>
       </c>
       <c r="E118">
-        <v>90380</v>
+        <v>90387</v>
       </c>
     </row>
     <row r="119" spans="1:5">
@@ -2377,10 +2377,10 @@
         <v>821019</v>
       </c>
       <c r="C119">
-        <v>526870</v>
+        <v>526961</v>
       </c>
       <c r="D119">
-        <v>840785</v>
+        <v>840932</v>
       </c>
       <c r="E119">
         <v>3071340</v>
@@ -2391,16 +2391,16 @@
         <v>119</v>
       </c>
       <c r="B120">
-        <v>11912725</v>
+        <v>11913577</v>
       </c>
       <c r="C120">
-        <v>10278886</v>
+        <v>10334826</v>
       </c>
       <c r="D120">
-        <v>18049287</v>
+        <v>18342637</v>
       </c>
       <c r="E120">
-        <v>57415735</v>
+        <v>57745803</v>
       </c>
     </row>
     <row r="121" spans="1:5">
@@ -2408,16 +2408,16 @@
         <v>120</v>
       </c>
       <c r="B121">
-        <v>23570177</v>
+        <v>23571863</v>
       </c>
       <c r="C121">
-        <v>28840758</v>
+        <v>28997715</v>
       </c>
       <c r="D121">
-        <v>34028404</v>
+        <v>34581459</v>
       </c>
       <c r="E121">
-        <v>32520023</v>
+        <v>32706972</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -2428,13 +2428,13 @@
         <v>26240283</v>
       </c>
       <c r="C122">
-        <v>33137234</v>
+        <v>33219873</v>
       </c>
       <c r="D122">
-        <v>37126227</v>
+        <v>37274208</v>
       </c>
       <c r="E122">
-        <v>30524131</v>
+        <v>30583550</v>
       </c>
     </row>
     <row r="123" spans="1:5">
@@ -2445,13 +2445,13 @@
         <v>24671607</v>
       </c>
       <c r="C123">
-        <v>29748220</v>
+        <v>29828616</v>
       </c>
       <c r="D123">
-        <v>27363110</v>
+        <v>27503571</v>
       </c>
       <c r="E123">
-        <v>14526865</v>
+        <v>14580626</v>
       </c>
     </row>
     <row r="124" spans="1:5">
@@ -2462,13 +2462,13 @@
         <v>7613984</v>
       </c>
       <c r="C124">
-        <v>8469581</v>
+        <v>8490702</v>
       </c>
       <c r="D124">
-        <v>15225924</v>
+        <v>15286614</v>
       </c>
       <c r="E124">
-        <v>39722069</v>
+        <v>39799394</v>
       </c>
     </row>
     <row r="125" spans="1:5">
@@ -2476,16 +2476,16 @@
         <v>124</v>
       </c>
       <c r="B125">
-        <v>26785441</v>
+        <v>26787424</v>
       </c>
       <c r="C125">
-        <v>35272554</v>
+        <v>35363188</v>
       </c>
       <c r="D125">
-        <v>40038907</v>
+        <v>40201633</v>
       </c>
       <c r="E125">
-        <v>32388031</v>
+        <v>32454157</v>
       </c>
     </row>
     <row r="126" spans="1:5">
@@ -2493,16 +2493,16 @@
         <v>125</v>
       </c>
       <c r="B126">
-        <v>1584622</v>
+        <v>1584695</v>
       </c>
       <c r="C126">
-        <v>1380669</v>
+        <v>1382257</v>
       </c>
       <c r="D126">
-        <v>1415055</v>
+        <v>1416896</v>
       </c>
       <c r="E126">
-        <v>1360667</v>
+        <v>1361397</v>
       </c>
     </row>
     <row r="127" spans="1:5">
@@ -2510,16 +2510,16 @@
         <v>126</v>
       </c>
       <c r="B127">
-        <v>29745224</v>
+        <v>29751607</v>
       </c>
       <c r="C127">
-        <v>34870535</v>
+        <v>34937104</v>
       </c>
       <c r="D127">
-        <v>38052126</v>
+        <v>38106044</v>
       </c>
       <c r="E127">
-        <v>32821515</v>
+        <v>32841243</v>
       </c>
     </row>
     <row r="128" spans="1:5">
@@ -2530,10 +2530,10 @@
         <v>2264451</v>
       </c>
       <c r="C128">
-        <v>895100</v>
+        <v>895304</v>
       </c>
       <c r="D128">
-        <v>1661608</v>
+        <v>1661866</v>
       </c>
       <c r="E128">
         <v>13407566</v>
@@ -2547,10 +2547,10 @@
         <v>2159128</v>
       </c>
       <c r="C129">
-        <v>1982007</v>
+        <v>1982458</v>
       </c>
       <c r="D129">
-        <v>3560588</v>
+        <v>3561142</v>
       </c>
       <c r="E129">
         <v>12156193</v>
@@ -2561,16 +2561,16 @@
         <v>129</v>
       </c>
       <c r="B130">
-        <v>12162592</v>
+        <v>12163366</v>
       </c>
       <c r="C130">
-        <v>13750239</v>
+        <v>13787471</v>
       </c>
       <c r="D130">
-        <v>14312936</v>
+        <v>14485249</v>
       </c>
       <c r="E130">
-        <v>11526027</v>
+        <v>11605120</v>
       </c>
     </row>
     <row r="131" spans="1:5">
@@ -2578,16 +2578,16 @@
         <v>130</v>
       </c>
       <c r="B131">
-        <v>20817552</v>
+        <v>20819094</v>
       </c>
       <c r="C131">
-        <v>24869650</v>
+        <v>24969949</v>
       </c>
       <c r="D131">
-        <v>25139121</v>
+        <v>25795990</v>
       </c>
       <c r="E131">
-        <v>18370530</v>
+        <v>18991060</v>
       </c>
     </row>
     <row r="132" spans="1:5">
@@ -2595,16 +2595,16 @@
         <v>131</v>
       </c>
       <c r="B132">
-        <v>36262549</v>
+        <v>36265207</v>
       </c>
       <c r="C132">
-        <v>37682455</v>
+        <v>37830615</v>
       </c>
       <c r="D132">
-        <v>35049439</v>
+        <v>35926474</v>
       </c>
       <c r="E132">
-        <v>24221822</v>
+        <v>24987542</v>
       </c>
     </row>
     <row r="133" spans="1:5">
@@ -2612,16 +2612,16 @@
         <v>132</v>
       </c>
       <c r="B133">
-        <v>12674807</v>
+        <v>12675689</v>
       </c>
       <c r="C133">
-        <v>13139456</v>
+        <v>13184852</v>
       </c>
       <c r="D133">
-        <v>14751124</v>
+        <v>15044334</v>
       </c>
       <c r="E133">
-        <v>15508091</v>
+        <v>15843988</v>
       </c>
     </row>
     <row r="134" spans="1:5">
@@ -2629,16 +2629,16 @@
         <v>133</v>
       </c>
       <c r="B134">
-        <v>5364975</v>
+        <v>5365856</v>
       </c>
       <c r="C134">
-        <v>6869608</v>
+        <v>6902491</v>
       </c>
       <c r="D134">
-        <v>12466323</v>
+        <v>12872810</v>
       </c>
       <c r="E134">
-        <v>32585585</v>
+        <v>33781026</v>
       </c>
     </row>
     <row r="135" spans="1:5">
@@ -2646,16 +2646,16 @@
         <v>134</v>
       </c>
       <c r="B135">
-        <v>37118977</v>
+        <v>37119557</v>
       </c>
       <c r="C135">
-        <v>41748226</v>
+        <v>41847045</v>
       </c>
       <c r="D135">
-        <v>43758646</v>
+        <v>44277111</v>
       </c>
       <c r="E135">
-        <v>36014205</v>
+        <v>36275694</v>
       </c>
     </row>
     <row r="136" spans="1:5">
@@ -2666,13 +2666,13 @@
         <v>29340056</v>
       </c>
       <c r="C136">
-        <v>33003935</v>
+        <v>33089689</v>
       </c>
       <c r="D136">
-        <v>37425090</v>
+        <v>37913246</v>
       </c>
       <c r="E136">
-        <v>36307726</v>
+        <v>36647782</v>
       </c>
     </row>
     <row r="137" spans="1:5">
@@ -2683,13 +2683,13 @@
         <v>14840033</v>
       </c>
       <c r="C137">
-        <v>15673422</v>
+        <v>15710830</v>
       </c>
       <c r="D137">
-        <v>18797193</v>
+        <v>18998317</v>
       </c>
       <c r="E137">
-        <v>21749763</v>
+        <v>21854538</v>
       </c>
     </row>
     <row r="138" spans="1:5">
@@ -2700,13 +2700,13 @@
         <v>23644212</v>
       </c>
       <c r="C138">
-        <v>31039521</v>
+        <v>31113605</v>
       </c>
       <c r="D138">
-        <v>31543235</v>
+        <v>31880737</v>
       </c>
       <c r="E138">
-        <v>20601008</v>
+        <v>20700249</v>
       </c>
     </row>
     <row r="139" spans="1:5">
@@ -2717,13 +2717,13 @@
         <v>19581755</v>
       </c>
       <c r="C139">
-        <v>21788707</v>
+        <v>21864446</v>
       </c>
       <c r="D139">
-        <v>22834252</v>
+        <v>23111166</v>
       </c>
       <c r="E139">
-        <v>18854039</v>
+        <v>18949449</v>
       </c>
     </row>
     <row r="140" spans="1:5">
@@ -2734,10 +2734,10 @@
         <v>5289565</v>
       </c>
       <c r="C140">
-        <v>6169657</v>
+        <v>6175245</v>
       </c>
       <c r="D140">
-        <v>6052871</v>
+        <v>6062385</v>
       </c>
       <c r="E140">
         <v>5256939</v>
@@ -2751,13 +2751,13 @@
         <v>36212835</v>
       </c>
       <c r="C141">
-        <v>48159152</v>
+        <v>48326556</v>
       </c>
       <c r="D141">
-        <v>54182971</v>
+        <v>54840055</v>
       </c>
       <c r="E141">
-        <v>43479723</v>
+        <v>43699750</v>
       </c>
     </row>
     <row r="142" spans="1:5">
@@ -2768,13 +2768,13 @@
         <v>11484694</v>
       </c>
       <c r="C142">
-        <v>12649199</v>
+        <v>12694925</v>
       </c>
       <c r="D142">
-        <v>13225679</v>
+        <v>13401808</v>
       </c>
       <c r="E142">
-        <v>10931371</v>
+        <v>11009946</v>
       </c>
     </row>
     <row r="143" spans="1:5">
@@ -2785,13 +2785,13 @@
         <v>798409</v>
       </c>
       <c r="C143">
-        <v>878524</v>
+        <v>881991</v>
       </c>
       <c r="D143">
-        <v>826457</v>
+        <v>839146</v>
       </c>
       <c r="E143">
-        <v>516772</v>
+        <v>527580</v>
       </c>
     </row>
     <row r="144" spans="1:5">
@@ -2802,13 +2802,13 @@
         <v>19351033</v>
       </c>
       <c r="C144">
-        <v>26298355</v>
+        <v>26350559</v>
       </c>
       <c r="D144">
-        <v>30983129</v>
+        <v>31087467</v>
       </c>
       <c r="E144">
-        <v>26812618</v>
+        <v>26858600</v>
       </c>
     </row>
     <row r="145" spans="1:5">
@@ -2819,13 +2819,13 @@
         <v>5936734</v>
       </c>
       <c r="C145">
-        <v>5868228</v>
+        <v>5879877</v>
       </c>
       <c r="D145">
-        <v>9956376</v>
+        <v>9989905</v>
       </c>
       <c r="E145">
-        <v>25273525</v>
+        <v>25316867</v>
       </c>
     </row>
     <row r="146" spans="1:5">
@@ -2836,10 +2836,10 @@
         <v>2606609</v>
       </c>
       <c r="C146">
-        <v>3396695</v>
+        <v>3397734</v>
       </c>
       <c r="D146">
-        <v>3921061</v>
+        <v>3922418</v>
       </c>
       <c r="E146">
         <v>3576965</v>
@@ -2853,13 +2853,13 @@
         <v>4687733</v>
       </c>
       <c r="C147">
-        <v>4808122</v>
+        <v>4810680</v>
       </c>
       <c r="D147">
-        <v>7527155</v>
+        <v>7533907</v>
       </c>
       <c r="E147">
-        <v>15337600</v>
+        <v>15344073</v>
       </c>
     </row>
     <row r="148" spans="1:5">
@@ -2870,13 +2870,13 @@
         <v>31323747</v>
       </c>
       <c r="C148">
-        <v>40657203</v>
+        <v>40692734</v>
       </c>
       <c r="D148">
-        <v>45908272</v>
+        <v>46028462</v>
       </c>
       <c r="E148">
-        <v>37672843</v>
+        <v>37732051</v>
       </c>
     </row>
     <row r="149" spans="1:5">
@@ -2887,13 +2887,13 @@
         <v>25768520</v>
       </c>
       <c r="C149">
-        <v>31614748</v>
+        <v>31650399</v>
       </c>
       <c r="D149">
-        <v>28352450</v>
+        <v>28675577</v>
       </c>
       <c r="E149">
-        <v>14087219</v>
+        <v>14160742</v>
       </c>
     </row>
     <row r="150" spans="1:5">
@@ -2904,13 +2904,13 @@
         <v>15698064</v>
       </c>
       <c r="C150">
-        <v>16260376</v>
+        <v>16278712</v>
       </c>
       <c r="D150">
-        <v>17629408</v>
+        <v>17830327</v>
       </c>
       <c r="E150">
-        <v>16714886</v>
+        <v>16802124</v>
       </c>
     </row>
     <row r="151" spans="1:5">
@@ -2921,13 +2921,13 @@
         <v>4100955</v>
       </c>
       <c r="C151">
-        <v>6160432</v>
+        <v>6168367</v>
       </c>
       <c r="D151">
-        <v>7687592</v>
+        <v>7806299</v>
       </c>
       <c r="E151">
-        <v>6762217</v>
+        <v>6851625</v>
       </c>
     </row>
     <row r="152" spans="1:5">
@@ -2938,13 +2938,13 @@
         <v>25514643</v>
       </c>
       <c r="C152">
-        <v>28419894</v>
+        <v>28451943</v>
       </c>
       <c r="D152">
-        <v>27322554</v>
+        <v>27633943</v>
       </c>
       <c r="E152">
-        <v>18174702</v>
+        <v>18269558</v>
       </c>
     </row>
     <row r="153" spans="1:5">
@@ -2952,13 +2952,13 @@
         <v>152</v>
       </c>
       <c r="B153">
-        <v>654053</v>
+        <v>654057</v>
       </c>
       <c r="C153">
-        <v>855599</v>
+        <v>856069</v>
       </c>
       <c r="D153">
-        <v>1250150</v>
+        <v>1250383</v>
       </c>
       <c r="E153">
         <v>1795069</v>
@@ -2969,13 +2969,13 @@
         <v>153</v>
       </c>
       <c r="B154">
-        <v>18967527</v>
+        <v>18967639</v>
       </c>
       <c r="C154">
-        <v>20762547</v>
+        <v>20773944</v>
       </c>
       <c r="D154">
-        <v>32430349</v>
+        <v>32436417</v>
       </c>
       <c r="E154">
         <v>62741930</v>
@@ -2989,13 +2989,13 @@
         <v>19320729</v>
       </c>
       <c r="C155">
-        <v>23886310</v>
+        <v>23925951</v>
       </c>
       <c r="D155">
-        <v>34149016</v>
+        <v>34268373</v>
       </c>
       <c r="E155">
-        <v>46228168</v>
+        <v>46308229</v>
       </c>
     </row>
     <row r="156" spans="1:5">
@@ -3006,13 +3006,13 @@
         <v>20997322</v>
       </c>
       <c r="C156">
-        <v>29315017</v>
+        <v>29363667</v>
       </c>
       <c r="D156">
-        <v>45325057</v>
+        <v>45483477</v>
       </c>
       <c r="E156">
-        <v>64139725</v>
+        <v>64250806</v>
       </c>
     </row>
     <row r="157" spans="1:5">
@@ -3023,13 +3023,13 @@
         <v>22943075</v>
       </c>
       <c r="C157">
-        <v>29568193</v>
+        <v>29596152</v>
       </c>
       <c r="D157">
-        <v>40765036</v>
+        <v>40812571</v>
       </c>
       <c r="E157">
-        <v>48743661</v>
+        <v>48765933</v>
       </c>
     </row>
     <row r="158" spans="1:5">
@@ -3040,13 +3040,13 @@
         <v>33998674</v>
       </c>
       <c r="C158">
-        <v>38886544</v>
+        <v>38930678</v>
       </c>
       <c r="D158">
-        <v>44434241</v>
+        <v>44575871</v>
       </c>
       <c r="E158">
-        <v>41615395</v>
+        <v>41689345</v>
       </c>
     </row>
     <row r="159" spans="1:5">
@@ -3057,13 +3057,13 @@
         <v>30031294</v>
       </c>
       <c r="C159">
-        <v>36581592</v>
+        <v>36663245</v>
       </c>
       <c r="D159">
-        <v>39723856</v>
+        <v>40223175</v>
       </c>
       <c r="E159">
-        <v>31598357</v>
+        <v>31775170</v>
       </c>
     </row>
     <row r="160" spans="1:5">
@@ -3074,13 +3074,13 @@
         <v>9580523</v>
       </c>
       <c r="C160">
-        <v>8742650</v>
+        <v>8751366</v>
       </c>
       <c r="D160">
-        <v>14741360</v>
+        <v>14794546</v>
       </c>
       <c r="E160">
-        <v>37858821</v>
+        <v>37932050</v>
       </c>
     </row>
     <row r="161" spans="1:5">
@@ -3091,13 +3091,13 @@
         <v>36007198</v>
       </c>
       <c r="C161">
-        <v>37281118</v>
+        <v>37339968</v>
       </c>
       <c r="D161">
-        <v>63629306</v>
+        <v>63705396</v>
       </c>
       <c r="E161">
-        <v>148493895</v>
+        <v>148572998</v>
       </c>
     </row>
     <row r="162" spans="1:5">
@@ -3108,10 +3108,10 @@
         <v>496590</v>
       </c>
       <c r="C162">
-        <v>556591</v>
+        <v>556703</v>
       </c>
       <c r="D162">
-        <v>724569</v>
+        <v>724731</v>
       </c>
       <c r="E162">
         <v>1101046</v>
@@ -3125,13 +3125,13 @@
         <v>30003950</v>
       </c>
       <c r="C163">
-        <v>35403007</v>
+        <v>35450737</v>
       </c>
       <c r="D163">
-        <v>33363627</v>
+        <v>33790335</v>
       </c>
       <c r="E163">
-        <v>19553503</v>
+        <v>19658369</v>
       </c>
     </row>
     <row r="164" spans="1:5">
@@ -3142,13 +3142,13 @@
         <v>3213930</v>
       </c>
       <c r="C164">
-        <v>2767900</v>
+        <v>2769792</v>
       </c>
       <c r="D164">
-        <v>4991697</v>
+        <v>5007590</v>
       </c>
       <c r="E164">
-        <v>17262093</v>
+        <v>17291538</v>
       </c>
     </row>
     <row r="165" spans="1:5">
@@ -3159,13 +3159,13 @@
         <v>34958636</v>
       </c>
       <c r="C165">
-        <v>42666099</v>
+        <v>42679308</v>
       </c>
       <c r="D165">
-        <v>45303611</v>
+        <v>45463053</v>
       </c>
       <c r="E165">
-        <v>33354575</v>
+        <v>33417680</v>
       </c>
     </row>
     <row r="166" spans="1:5">
@@ -3176,13 +3176,13 @@
         <v>10996008</v>
       </c>
       <c r="C166">
-        <v>15910998</v>
+        <v>15915924</v>
       </c>
       <c r="D166">
-        <v>25042830</v>
+        <v>25130966</v>
       </c>
       <c r="E166">
-        <v>35462764</v>
+        <v>35529858</v>
       </c>
     </row>
     <row r="167" spans="1:5">
@@ -3190,16 +3190,16 @@
         <v>166</v>
       </c>
       <c r="B167">
-        <v>84037</v>
+        <v>84038</v>
       </c>
       <c r="C167">
-        <v>103940</v>
+        <v>104221</v>
       </c>
       <c r="D167">
-        <v>69589</v>
+        <v>69677</v>
       </c>
       <c r="E167">
-        <v>81514</v>
+        <v>81557</v>
       </c>
     </row>
     <row r="168" spans="1:5">
@@ -3207,16 +3207,16 @@
         <v>167</v>
       </c>
       <c r="B168">
-        <v>991679</v>
+        <v>991681</v>
       </c>
       <c r="C168">
-        <v>1235243</v>
+        <v>1235730</v>
       </c>
       <c r="D168">
-        <v>1450212</v>
+        <v>1450415</v>
       </c>
       <c r="E168">
-        <v>1308433</v>
+        <v>1308551</v>
       </c>
     </row>
     <row r="169" spans="1:5">
@@ -3224,16 +3224,16 @@
         <v>168</v>
       </c>
       <c r="B169">
-        <v>17838340</v>
+        <v>17838784</v>
       </c>
       <c r="C169">
-        <v>19716558</v>
+        <v>19797230</v>
       </c>
       <c r="D169">
-        <v>30425573</v>
+        <v>30839525</v>
       </c>
       <c r="E169">
-        <v>57037274</v>
+        <v>57409318</v>
       </c>
     </row>
     <row r="170" spans="1:5">
@@ -3244,13 +3244,13 @@
         <v>20984373</v>
       </c>
       <c r="C170">
-        <v>24243861</v>
+        <v>24269530</v>
       </c>
       <c r="D170">
-        <v>34652920</v>
+        <v>35128805</v>
       </c>
       <c r="E170">
-        <v>52718450</v>
+        <v>53520419</v>
       </c>
     </row>
     <row r="171" spans="1:5">
@@ -3258,16 +3258,16 @@
         <v>170</v>
       </c>
       <c r="B171">
-        <v>3668851</v>
+        <v>3668942</v>
       </c>
       <c r="C171">
-        <v>3803958</v>
+        <v>3819112</v>
       </c>
       <c r="D171">
-        <v>5814078</v>
+        <v>5888287</v>
       </c>
       <c r="E171">
-        <v>11144062</v>
+        <v>11200768</v>
       </c>
     </row>
     <row r="172" spans="1:5">
@@ -3278,13 +3278,13 @@
         <v>10439073</v>
       </c>
       <c r="C172">
-        <v>14063329</v>
+        <v>14075647</v>
       </c>
       <c r="D172">
-        <v>17526590</v>
+        <v>17684833</v>
       </c>
       <c r="E172">
-        <v>17074161</v>
+        <v>17153793</v>
       </c>
     </row>
     <row r="173" spans="1:5">
@@ -3295,13 +3295,13 @@
         <v>24642068</v>
       </c>
       <c r="C173">
-        <v>29327314</v>
+        <v>29362830</v>
       </c>
       <c r="D173">
-        <v>36871881</v>
+        <v>37526128</v>
       </c>
       <c r="E173">
-        <v>42300099</v>
+        <v>43332275</v>
       </c>
     </row>
     <row r="174" spans="1:5">
@@ -3309,16 +3309,16 @@
         <v>173</v>
       </c>
       <c r="B174">
-        <v>9959320</v>
+        <v>9959649</v>
       </c>
       <c r="C174">
-        <v>15141243</v>
+        <v>15167764</v>
       </c>
       <c r="D174">
-        <v>24798640</v>
+        <v>25303308</v>
       </c>
       <c r="E174">
-        <v>40327634</v>
+        <v>41561392</v>
       </c>
     </row>
     <row r="175" spans="1:5">
@@ -3326,16 +3326,16 @@
         <v>174</v>
       </c>
       <c r="B175">
-        <v>492551</v>
+        <v>492557</v>
       </c>
       <c r="C175">
-        <v>532402</v>
+        <v>532751</v>
       </c>
       <c r="D175">
-        <v>679289</v>
+        <v>679914</v>
       </c>
       <c r="E175">
-        <v>860589</v>
+        <v>860962</v>
       </c>
     </row>
     <row r="176" spans="1:5">
@@ -3343,16 +3343,16 @@
         <v>175</v>
       </c>
       <c r="B176">
-        <v>28001928</v>
+        <v>28002455</v>
       </c>
       <c r="C176">
-        <v>33251429</v>
+        <v>33292506</v>
       </c>
       <c r="D176">
-        <v>39652077</v>
+        <v>39759391</v>
       </c>
       <c r="E176">
-        <v>39975919</v>
+        <v>40040563</v>
       </c>
     </row>
     <row r="177" spans="1:5">
@@ -3360,16 +3360,16 @@
         <v>176</v>
       </c>
       <c r="B177">
-        <v>23679792</v>
+        <v>23680237</v>
       </c>
       <c r="C177">
-        <v>30512431</v>
+        <v>30550125</v>
       </c>
       <c r="D177">
-        <v>35707999</v>
+        <v>35804638</v>
       </c>
       <c r="E177">
-        <v>31931484</v>
+        <v>31983119</v>
       </c>
     </row>
     <row r="178" spans="1:5">
@@ -3377,16 +3377,16 @@
         <v>177</v>
       </c>
       <c r="B178">
-        <v>19758811</v>
+        <v>19758992</v>
       </c>
       <c r="C178">
-        <v>23648113</v>
+        <v>23680971</v>
       </c>
       <c r="D178">
-        <v>23593146</v>
+        <v>23826215</v>
       </c>
       <c r="E178">
-        <v>16112256</v>
+        <v>16190149</v>
       </c>
     </row>
     <row r="179" spans="1:5">
@@ -3394,16 +3394,16 @@
         <v>178</v>
       </c>
       <c r="B179">
-        <v>3225506</v>
+        <v>3225513</v>
       </c>
       <c r="C179">
-        <v>2830686</v>
+        <v>2833182</v>
       </c>
       <c r="D179">
-        <v>6194960</v>
+        <v>6209815</v>
       </c>
       <c r="E179">
-        <v>49808973</v>
+        <v>49889531</v>
       </c>
     </row>
     <row r="180" spans="1:5">
@@ -3414,13 +3414,13 @@
         <v>913089</v>
       </c>
       <c r="C180">
-        <v>1102822</v>
+        <v>1102879</v>
       </c>
       <c r="D180">
-        <v>1372233</v>
+        <v>1372370</v>
       </c>
       <c r="E180">
-        <v>1530999</v>
+        <v>1531100</v>
       </c>
     </row>
     <row r="181" spans="1:5">
@@ -3431,13 +3431,13 @@
         <v>107422</v>
       </c>
       <c r="C181">
-        <v>64872</v>
+        <v>64875</v>
       </c>
       <c r="D181">
-        <v>80720</v>
+        <v>80728</v>
       </c>
       <c r="E181">
-        <v>180118</v>
+        <v>180129</v>
       </c>
     </row>
     <row r="182" spans="1:5">
@@ -3448,13 +3448,13 @@
         <v>144192</v>
       </c>
       <c r="C182">
-        <v>175578</v>
+        <v>175595</v>
       </c>
       <c r="D182">
-        <v>226753</v>
+        <v>226789</v>
       </c>
       <c r="E182">
-        <v>259478</v>
+        <v>259500</v>
       </c>
     </row>
     <row r="183" spans="1:5">
@@ -3465,13 +3465,13 @@
         <v>226479</v>
       </c>
       <c r="C183">
-        <v>219351</v>
+        <v>219352</v>
       </c>
       <c r="D183">
-        <v>361539</v>
+        <v>361592</v>
       </c>
       <c r="E183">
-        <v>1095845</v>
+        <v>1095937</v>
       </c>
     </row>
     <row r="184" spans="1:5">
@@ -3482,13 +3482,13 @@
         <v>280675</v>
       </c>
       <c r="C184">
-        <v>282091</v>
+        <v>282224</v>
       </c>
       <c r="D184">
-        <v>438527</v>
+        <v>438986</v>
       </c>
       <c r="E184">
-        <v>1346796</v>
+        <v>1347438</v>
       </c>
     </row>
     <row r="185" spans="1:5">
@@ -3499,13 +3499,13 @@
         <v>28301388</v>
       </c>
       <c r="C185">
-        <v>26911522</v>
+        <v>26924146</v>
       </c>
       <c r="D185">
-        <v>48530298</v>
+        <v>48581082</v>
       </c>
       <c r="E185">
-        <v>149157691</v>
+        <v>149228706</v>
       </c>
     </row>
     <row r="186" spans="1:5">
@@ -3516,10 +3516,10 @@
         <v>16809106</v>
       </c>
       <c r="C186">
-        <v>16746987</v>
+        <v>16748565</v>
       </c>
       <c r="D186">
-        <v>26446489</v>
+        <v>26452554</v>
       </c>
       <c r="E186">
         <v>57570010</v>
@@ -3533,13 +3533,13 @@
         <v>9366572</v>
       </c>
       <c r="C187">
-        <v>9549393</v>
+        <v>9553570</v>
       </c>
       <c r="D187">
-        <v>19007505</v>
+        <v>19031556</v>
       </c>
       <c r="E187">
-        <v>71764894</v>
+        <v>71801076</v>
       </c>
     </row>
     <row r="188" spans="1:5">
@@ -3550,10 +3550,10 @@
         <v>92234</v>
       </c>
       <c r="C188">
-        <v>113467</v>
+        <v>113511</v>
       </c>
       <c r="D188">
-        <v>147517</v>
+        <v>147551</v>
       </c>
       <c r="E188">
         <v>429208</v>
@@ -3567,13 +3567,13 @@
         <v>47704</v>
       </c>
       <c r="C189">
-        <v>58276</v>
+        <v>58290</v>
       </c>
       <c r="D189">
-        <v>75610</v>
+        <v>75622</v>
       </c>
       <c r="E189">
-        <v>86603</v>
+        <v>86611</v>
       </c>
     </row>
     <row r="190" spans="1:5">
@@ -3584,13 +3584,13 @@
         <v>47704</v>
       </c>
       <c r="C190">
-        <v>58276</v>
+        <v>58290</v>
       </c>
       <c r="D190">
-        <v>75610</v>
+        <v>75622</v>
       </c>
       <c r="E190">
-        <v>173207</v>
+        <v>173222</v>
       </c>
     </row>
     <row r="191" spans="1:5">
@@ -3598,16 +3598,16 @@
         <v>190</v>
       </c>
       <c r="B191">
-        <v>1598004</v>
+        <v>1598011</v>
       </c>
       <c r="C191">
-        <v>1417778</v>
+        <v>1418956</v>
       </c>
       <c r="D191">
-        <v>2858807</v>
+        <v>2862007</v>
       </c>
       <c r="E191">
-        <v>12897274</v>
+        <v>12903405</v>
       </c>
     </row>
     <row r="192" spans="1:5">
@@ -3618,13 +3618,13 @@
         <v>3622919</v>
       </c>
       <c r="C192">
-        <v>4427931</v>
+        <v>4429868</v>
       </c>
       <c r="D192">
-        <v>8206192</v>
+        <v>8216576</v>
       </c>
       <c r="E192">
-        <v>20025511</v>
+        <v>20035608</v>
       </c>
     </row>
     <row r="193" spans="1:5">
@@ -3635,13 +3635,13 @@
         <v>21711227</v>
       </c>
       <c r="C193">
-        <v>19529066</v>
+        <v>19583864</v>
       </c>
       <c r="D193">
-        <v>28286196</v>
+        <v>28617092</v>
       </c>
       <c r="E193">
-        <v>56111730</v>
+        <v>56397031</v>
       </c>
     </row>
     <row r="194" spans="1:5">
@@ -3652,13 +3652,13 @@
         <v>14589713</v>
       </c>
       <c r="C194">
-        <v>17172963</v>
+        <v>17241192</v>
       </c>
       <c r="D194">
-        <v>23304849</v>
+        <v>23862524</v>
       </c>
       <c r="E194">
-        <v>31197368</v>
+        <v>32079804</v>
       </c>
     </row>
     <row r="195" spans="1:5">
@@ -3666,16 +3666,16 @@
         <v>194</v>
       </c>
       <c r="B195">
-        <v>7465542</v>
+        <v>7465730</v>
       </c>
       <c r="C195">
-        <v>10378550</v>
+        <v>10422703</v>
       </c>
       <c r="D195">
-        <v>11075670</v>
+        <v>11240477</v>
       </c>
       <c r="E195">
-        <v>7683732</v>
+        <v>7750592</v>
       </c>
     </row>
     <row r="196" spans="1:5">
@@ -3686,13 +3686,13 @@
         <v>23458928</v>
       </c>
       <c r="C196">
-        <v>30001474</v>
+        <v>30085925</v>
       </c>
       <c r="D196">
-        <v>28735959</v>
+        <v>29075467</v>
       </c>
       <c r="E196">
-        <v>16373415</v>
+        <v>16459872</v>
       </c>
     </row>
     <row r="197" spans="1:5">
@@ -3703,13 +3703,13 @@
         <v>19240299</v>
       </c>
       <c r="C197">
-        <v>21980929</v>
+        <v>22023896</v>
       </c>
       <c r="D197">
-        <v>24098935</v>
+        <v>24386895</v>
       </c>
       <c r="E197">
-        <v>20833928</v>
+        <v>20950530</v>
       </c>
     </row>
     <row r="198" spans="1:5">
@@ -3720,13 +3720,13 @@
         <v>6103184</v>
       </c>
       <c r="C198">
-        <v>7879013</v>
+        <v>7897672</v>
       </c>
       <c r="D198">
-        <v>11572255</v>
+        <v>11783278</v>
       </c>
       <c r="E198">
-        <v>16170807</v>
+        <v>16466424</v>
       </c>
     </row>
     <row r="199" spans="1:5">
@@ -3737,13 +3737,13 @@
         <v>25793000</v>
       </c>
       <c r="C199">
-        <v>33442321</v>
+        <v>33481621</v>
       </c>
       <c r="D199">
-        <v>35715412</v>
+        <v>35888823</v>
       </c>
       <c r="E199">
-        <v>25911658</v>
+        <v>26059276</v>
       </c>
     </row>
     <row r="200" spans="1:5">
@@ -3754,13 +3754,13 @@
         <v>24190815</v>
       </c>
       <c r="C200">
-        <v>29648626</v>
+        <v>29677821</v>
       </c>
       <c r="D200">
-        <v>31609473</v>
+        <v>31701037</v>
       </c>
       <c r="E200">
-        <v>23816161</v>
+        <v>23859618</v>
       </c>
     </row>
     <row r="201" spans="1:5">
@@ -3771,13 +3771,13 @@
         <v>229222</v>
       </c>
       <c r="C201">
-        <v>280389</v>
+        <v>280699</v>
       </c>
       <c r="D201">
-        <v>360352</v>
+        <v>361726</v>
       </c>
       <c r="E201">
-        <v>246331</v>
+        <v>247081</v>
       </c>
     </row>
     <row r="202" spans="1:5">
@@ -3788,10 +3788,10 @@
         <v>47278</v>
       </c>
       <c r="C202">
-        <v>58545</v>
+        <v>58557</v>
       </c>
       <c r="D202">
-        <v>71938</v>
+        <v>71991</v>
       </c>
       <c r="E202">
         <v>82481</v>
@@ -3805,13 +3805,13 @@
         <v>20897114</v>
       </c>
       <c r="C203">
-        <v>25878617</v>
+        <v>25915574</v>
       </c>
       <c r="D203">
-        <v>36989272</v>
+        <v>37095702</v>
       </c>
       <c r="E203">
-        <v>50865898</v>
+        <v>50952873</v>
       </c>
     </row>
     <row r="204" spans="1:5">
@@ -3819,16 +3819,16 @@
         <v>203</v>
       </c>
       <c r="B204">
-        <v>23452980</v>
+        <v>23454680</v>
       </c>
       <c r="C204">
-        <v>27880951</v>
+        <v>27938943</v>
       </c>
       <c r="D204">
-        <v>34703436</v>
+        <v>34820158</v>
       </c>
       <c r="E204">
-        <v>37214471</v>
+        <v>37286717</v>
       </c>
     </row>
     <row r="205" spans="1:5">
@@ -3836,16 +3836,16 @@
         <v>204</v>
       </c>
       <c r="B205">
-        <v>4018374</v>
+        <v>4018571</v>
       </c>
       <c r="C205">
-        <v>3472581</v>
+        <v>3475764</v>
       </c>
       <c r="D205">
-        <v>5942136</v>
+        <v>5948861</v>
       </c>
       <c r="E205">
-        <v>17799983</v>
+        <v>17809010</v>
       </c>
     </row>
     <row r="206" spans="1:5">
@@ -3853,16 +3853,16 @@
         <v>205</v>
       </c>
       <c r="B206">
-        <v>9020829</v>
+        <v>9024729</v>
       </c>
       <c r="C206">
-        <v>13002129</v>
+        <v>13129118</v>
       </c>
       <c r="D206">
-        <v>14576447</v>
+        <v>15003843</v>
       </c>
       <c r="E206">
-        <v>7014489</v>
+        <v>7103814</v>
       </c>
     </row>
     <row r="207" spans="1:5">
@@ -3870,16 +3870,16 @@
         <v>206</v>
       </c>
       <c r="B207">
-        <v>10598000</v>
+        <v>10598886</v>
       </c>
       <c r="C207">
-        <v>12174750</v>
+        <v>12240012</v>
       </c>
       <c r="D207">
-        <v>12853387</v>
+        <v>13162727</v>
       </c>
       <c r="E207">
-        <v>5988262</v>
+        <v>6061871</v>
       </c>
     </row>
     <row r="208" spans="1:5">
@@ -3887,16 +3887,16 @@
         <v>207</v>
       </c>
       <c r="B208">
-        <v>14909051</v>
+        <v>14910297</v>
       </c>
       <c r="C208">
-        <v>19567434</v>
+        <v>19672324</v>
       </c>
       <c r="D208">
-        <v>23795036</v>
+        <v>24367706</v>
       </c>
       <c r="E208">
-        <v>15755524</v>
+        <v>15949194</v>
       </c>
     </row>
     <row r="209" spans="1:5">
@@ -3904,16 +3904,16 @@
         <v>208</v>
       </c>
       <c r="B209">
-        <v>2474289</v>
+        <v>2475469</v>
       </c>
       <c r="C209">
-        <v>4214373</v>
+        <v>4269042</v>
       </c>
       <c r="D209">
-        <v>5018984</v>
+        <v>5286200</v>
       </c>
       <c r="E209">
-        <v>2656954</v>
+        <v>2802610</v>
       </c>
     </row>
     <row r="210" spans="1:5">
@@ -3921,16 +3921,16 @@
         <v>209</v>
       </c>
       <c r="B210">
-        <v>11077006</v>
+        <v>11077931</v>
       </c>
       <c r="C210">
-        <v>15883291</v>
+        <v>15968432</v>
       </c>
       <c r="D210">
-        <v>21679922</v>
+        <v>22201687</v>
       </c>
       <c r="E210">
-        <v>17325263</v>
+        <v>17538228</v>
       </c>
     </row>
     <row r="211" spans="1:5">
@@ -3938,16 +3938,16 @@
         <v>210</v>
       </c>
       <c r="B211">
-        <v>5600759</v>
+        <v>5600766</v>
       </c>
       <c r="C211">
-        <v>9816061</v>
+        <v>9835736</v>
       </c>
       <c r="D211">
-        <v>14879467</v>
+        <v>14949902</v>
       </c>
       <c r="E211">
-        <v>11914210</v>
+        <v>11960233</v>
       </c>
     </row>
     <row r="212" spans="1:5">
@@ -3955,16 +3955,16 @@
         <v>211</v>
       </c>
       <c r="B212">
-        <v>3504751</v>
+        <v>3505029</v>
       </c>
       <c r="C212">
-        <v>5311605</v>
+        <v>5331289</v>
       </c>
       <c r="D212">
-        <v>9458795</v>
+        <v>9520335</v>
       </c>
       <c r="E212">
-        <v>13294403</v>
+        <v>13348070</v>
       </c>
     </row>
     <row r="213" spans="1:5">
@@ -3972,16 +3972,16 @@
         <v>212</v>
       </c>
       <c r="B213">
-        <v>9719823</v>
+        <v>9720635</v>
       </c>
       <c r="C213">
-        <v>13077487</v>
+        <v>13147588</v>
       </c>
       <c r="D213">
-        <v>14643099</v>
+        <v>14995511</v>
       </c>
       <c r="E213">
-        <v>7325447</v>
+        <v>7415492</v>
       </c>
     </row>
     <row r="214" spans="1:5">
@@ -3992,13 +3992,13 @@
         <v>9683253</v>
       </c>
       <c r="C214">
-        <v>13498897</v>
+        <v>13509034</v>
       </c>
       <c r="D214">
-        <v>15177310</v>
+        <v>15230342</v>
       </c>
       <c r="E214">
-        <v>6512703</v>
+        <v>6535976</v>
       </c>
     </row>
     <row r="215" spans="1:5">
@@ -4009,13 +4009,13 @@
         <v>10068152</v>
       </c>
       <c r="C215">
-        <v>14992949</v>
+        <v>15004209</v>
       </c>
       <c r="D215">
-        <v>18585388</v>
+        <v>18650329</v>
       </c>
       <c r="E215">
-        <v>10199139</v>
+        <v>10235585</v>
       </c>
     </row>
     <row r="216" spans="1:5">
@@ -4026,13 +4026,13 @@
         <v>15427203</v>
       </c>
       <c r="C216">
-        <v>20531103</v>
+        <v>20543129</v>
       </c>
       <c r="D216">
-        <v>22678459</v>
+        <v>22751924</v>
       </c>
       <c r="E216">
-        <v>9156430</v>
+        <v>9187563</v>
       </c>
     </row>
     <row r="217" spans="1:5">
@@ -4043,13 +4043,13 @@
         <v>11992119</v>
       </c>
       <c r="C217">
-        <v>18188775</v>
+        <v>18209460</v>
       </c>
       <c r="D217">
-        <v>24153688</v>
+        <v>24249436</v>
       </c>
       <c r="E217">
-        <v>15727974</v>
+        <v>15786820</v>
       </c>
     </row>
     <row r="218" spans="1:5">
@@ -4060,13 +4060,13 @@
         <v>14183640</v>
       </c>
       <c r="C218">
-        <v>22677479</v>
+        <v>22688875</v>
       </c>
       <c r="D218">
-        <v>30143578</v>
+        <v>30186376</v>
       </c>
       <c r="E218">
-        <v>20262367</v>
+        <v>20284154</v>
       </c>
     </row>
     <row r="219" spans="1:5">
@@ -4077,13 +4077,13 @@
         <v>13496999</v>
       </c>
       <c r="C219">
-        <v>19760539</v>
+        <v>19795322</v>
       </c>
       <c r="D219">
-        <v>26990519</v>
+        <v>27135421</v>
       </c>
       <c r="E219">
-        <v>22541297</v>
+        <v>22629335</v>
       </c>
     </row>
     <row r="220" spans="1:5">
@@ -4091,16 +4091,16 @@
         <v>219</v>
       </c>
       <c r="B220">
-        <v>8926874</v>
+        <v>8929640</v>
       </c>
       <c r="C220">
-        <v>13968639</v>
+        <v>14038427</v>
       </c>
       <c r="D220">
-        <v>21502738</v>
+        <v>21658416</v>
       </c>
       <c r="E220">
-        <v>22594796</v>
+        <v>22685948</v>
       </c>
     </row>
     <row r="221" spans="1:5">
@@ -4111,13 +4111,13 @@
         <v>15671489</v>
       </c>
       <c r="C221">
-        <v>22461871</v>
+        <v>22478379</v>
       </c>
       <c r="D221">
-        <v>34252129</v>
+        <v>34315168</v>
       </c>
       <c r="E221">
-        <v>40313943</v>
+        <v>40355307</v>
       </c>
     </row>
     <row r="222" spans="1:5">
@@ -4128,13 +4128,13 @@
         <v>5280362</v>
       </c>
       <c r="C222">
-        <v>7890841</v>
+        <v>7904731</v>
       </c>
       <c r="D222">
-        <v>11675979</v>
+        <v>11738663</v>
       </c>
       <c r="E222">
-        <v>11305542</v>
+        <v>11349698</v>
       </c>
     </row>
     <row r="223" spans="1:5">
@@ -4145,13 +4145,13 @@
         <v>334490</v>
       </c>
       <c r="C223">
-        <v>468482</v>
+        <v>468540</v>
       </c>
       <c r="D223">
-        <v>585558</v>
+        <v>585715</v>
       </c>
       <c r="E223">
-        <v>592327</v>
+        <v>592463</v>
       </c>
     </row>
     <row r="224" spans="1:5">
@@ -4162,10 +4162,10 @@
         <v>11781194</v>
       </c>
       <c r="C224">
-        <v>18123229</v>
+        <v>18124019</v>
       </c>
       <c r="D224">
-        <v>31607620</v>
+        <v>31612310</v>
       </c>
       <c r="E224">
         <v>39947574</v>
@@ -4179,13 +4179,13 @@
         <v>8414821</v>
       </c>
       <c r="C225">
-        <v>13658120</v>
+        <v>13662642</v>
       </c>
       <c r="D225">
-        <v>20206782</v>
+        <v>20255095</v>
       </c>
       <c r="E225">
-        <v>14750971</v>
+        <v>14795505</v>
       </c>
     </row>
     <row r="226" spans="1:5">
@@ -4196,13 +4196,13 @@
         <v>8216692</v>
       </c>
       <c r="C226">
-        <v>12249738</v>
+        <v>12251658</v>
       </c>
       <c r="D226">
-        <v>20075087</v>
+        <v>20091795</v>
       </c>
       <c r="E226">
-        <v>20338589</v>
+        <v>20356633</v>
       </c>
     </row>
     <row r="227" spans="1:5">
@@ -4213,13 +4213,13 @@
         <v>1136164</v>
       </c>
       <c r="C227">
-        <v>569176</v>
+        <v>569731</v>
       </c>
       <c r="D227">
-        <v>485686</v>
+        <v>490084</v>
       </c>
       <c r="E227">
-        <v>101660</v>
+        <v>104185</v>
       </c>
     </row>
     <row r="228" spans="1:5">
@@ -4230,10 +4230,10 @@
         <v>388636</v>
       </c>
       <c r="C228">
-        <v>616367</v>
+        <v>616384</v>
       </c>
       <c r="D228">
-        <v>1060013</v>
+        <v>1060123</v>
       </c>
       <c r="E228">
         <v>1043057</v>
@@ -4244,16 +4244,16 @@
         <v>228</v>
       </c>
       <c r="B229">
-        <v>17021583</v>
+        <v>17026855</v>
       </c>
       <c r="C229">
-        <v>25946835</v>
+        <v>26076467</v>
       </c>
       <c r="D229">
-        <v>31198932</v>
+        <v>31424811</v>
       </c>
       <c r="E229">
-        <v>19418530</v>
+        <v>19496869</v>
       </c>
     </row>
     <row r="230" spans="1:5">
@@ -4264,13 +4264,13 @@
         <v>3417535</v>
       </c>
       <c r="C230">
-        <v>4804574</v>
+        <v>4812131</v>
       </c>
       <c r="D230">
-        <v>5198886</v>
+        <v>5226791</v>
       </c>
       <c r="E230">
-        <v>2608311</v>
+        <v>2617946</v>
       </c>
     </row>
     <row r="231" spans="1:5">
@@ -4278,16 +4278,16 @@
         <v>230</v>
       </c>
       <c r="B231">
-        <v>4186940</v>
+        <v>4187133</v>
       </c>
       <c r="C231">
-        <v>5469028</v>
+        <v>5477519</v>
       </c>
       <c r="D231">
-        <v>10531110</v>
+        <v>10555838</v>
       </c>
       <c r="E231">
-        <v>22109287</v>
+        <v>22133766</v>
       </c>
     </row>
     <row r="232" spans="1:5">
@@ -4298,13 +4298,13 @@
         <v>4013916</v>
       </c>
       <c r="C232">
-        <v>4929944</v>
+        <v>4933107</v>
       </c>
       <c r="D232">
-        <v>10046547</v>
+        <v>10064036</v>
       </c>
       <c r="E232">
-        <v>23572472</v>
+        <v>23598901</v>
       </c>
     </row>
     <row r="233" spans="1:5">
@@ -4315,13 +4315,13 @@
         <v>382801</v>
       </c>
       <c r="C233">
-        <v>510138</v>
+        <v>510192</v>
       </c>
       <c r="D233">
-        <v>897975</v>
+        <v>898282</v>
       </c>
       <c r="E233">
-        <v>2042657</v>
+        <v>2043247</v>
       </c>
     </row>
     <row r="234" spans="1:5">
@@ -4332,10 +4332,10 @@
         <v>19247484</v>
       </c>
       <c r="C234">
-        <v>24617872</v>
+        <v>24624092</v>
       </c>
       <c r="D234">
-        <v>39681393</v>
+        <v>39695081</v>
       </c>
       <c r="E234">
         <v>66046827</v>
@@ -4349,10 +4349,10 @@
         <v>942185</v>
       </c>
       <c r="C235">
-        <v>1348924</v>
+        <v>1349265</v>
       </c>
       <c r="D235">
-        <v>2293320</v>
+        <v>2294112</v>
       </c>
       <c r="E235">
         <v>4040318</v>
@@ -4366,13 +4366,13 @@
         <v>1575901</v>
       </c>
       <c r="C236">
-        <v>2121027</v>
+        <v>2121322</v>
       </c>
       <c r="D236">
-        <v>3228757</v>
+        <v>3229537</v>
       </c>
       <c r="E236">
-        <v>4421436</v>
+        <v>4422528</v>
       </c>
     </row>
     <row r="237" spans="1:5">
@@ -4383,13 +4383,13 @@
         <v>9596737</v>
       </c>
       <c r="C237">
-        <v>17878871</v>
+        <v>17883687</v>
       </c>
       <c r="D237">
-        <v>27590094</v>
+        <v>27616898</v>
       </c>
       <c r="E237">
-        <v>20187540</v>
+        <v>20205523</v>
       </c>
     </row>
     <row r="238" spans="1:5">
@@ -4400,13 +4400,13 @@
         <v>14483547</v>
       </c>
       <c r="C238">
-        <v>22475667</v>
+        <v>22489188</v>
       </c>
       <c r="D238">
-        <v>35400069</v>
+        <v>35497969</v>
       </c>
       <c r="E238">
-        <v>31745142</v>
+        <v>31842141</v>
       </c>
     </row>
     <row r="239" spans="1:5">
@@ -4417,13 +4417,13 @@
         <v>222975</v>
       </c>
       <c r="C239">
-        <v>425656</v>
+        <v>425668</v>
       </c>
       <c r="D239">
-        <v>652739</v>
+        <v>652837</v>
       </c>
       <c r="E239">
-        <v>524518</v>
+        <v>524653</v>
       </c>
     </row>
     <row r="240" spans="1:5">
@@ -4434,10 +4434,10 @@
         <v>14606314</v>
       </c>
       <c r="C240">
-        <v>17683405</v>
+        <v>17684251</v>
       </c>
       <c r="D240">
-        <v>36191271</v>
+        <v>36197639</v>
       </c>
       <c r="E240">
         <v>81551942</v>
@@ -4451,13 +4451,13 @@
         <v>192495</v>
       </c>
       <c r="C241">
-        <v>241671</v>
+        <v>241677</v>
       </c>
       <c r="D241">
-        <v>525481</v>
+        <v>525559</v>
       </c>
       <c r="E241">
-        <v>1107174</v>
+        <v>1107448</v>
       </c>
     </row>
     <row r="242" spans="1:5">
@@ -4468,13 +4468,13 @@
         <v>5123948</v>
       </c>
       <c r="C242">
-        <v>5209154</v>
+        <v>5212982</v>
       </c>
       <c r="D242">
-        <v>10040513</v>
+        <v>10058992</v>
       </c>
       <c r="E242">
-        <v>27055820</v>
+        <v>27083581</v>
       </c>
     </row>
     <row r="243" spans="1:5">
@@ -4482,16 +4482,16 @@
         <v>242</v>
       </c>
       <c r="B243">
-        <v>10777091</v>
+        <v>10777093</v>
       </c>
       <c r="C243">
-        <v>14967508</v>
+        <v>14994481</v>
       </c>
       <c r="D243">
-        <v>27557100</v>
+        <v>27613386</v>
       </c>
       <c r="E243">
-        <v>53125134</v>
+        <v>53173438</v>
       </c>
     </row>
     <row r="244" spans="1:5">
@@ -4502,13 +4502,13 @@
         <v>12375382</v>
       </c>
       <c r="C244">
-        <v>13252087</v>
+        <v>13261826</v>
       </c>
       <c r="D244">
-        <v>25291925</v>
+        <v>25338473</v>
       </c>
       <c r="E244">
-        <v>63669822</v>
+        <v>63735151</v>
       </c>
     </row>
     <row r="245" spans="1:5">
@@ -4516,13 +4516,13 @@
         <v>244</v>
       </c>
       <c r="B245">
-        <v>13650547</v>
+        <v>13650548</v>
       </c>
       <c r="C245">
-        <v>16759718</v>
+        <v>16770510</v>
       </c>
       <c r="D245">
-        <v>29337453</v>
+        <v>29348635</v>
       </c>
       <c r="E245">
         <v>64667992</v>
@@ -4533,13 +4533,13 @@
         <v>245</v>
       </c>
       <c r="B246">
-        <v>151421</v>
+        <v>151422</v>
       </c>
       <c r="C246">
-        <v>212667</v>
+        <v>212802</v>
       </c>
       <c r="D246">
-        <v>367142</v>
+        <v>367293</v>
       </c>
       <c r="E246">
         <v>767693</v>
@@ -4550,13 +4550,13 @@
         <v>246</v>
       </c>
       <c r="B247">
-        <v>37855</v>
+        <v>37856</v>
       </c>
       <c r="C247">
-        <v>53167</v>
+        <v>53200</v>
       </c>
       <c r="D247">
-        <v>73428</v>
+        <v>73459</v>
       </c>
       <c r="E247">
         <v>170598</v>
@@ -4570,10 +4570,10 @@
         <v>1473826</v>
       </c>
       <c r="C248">
-        <v>2201937</v>
+        <v>2202383</v>
       </c>
       <c r="D248">
-        <v>2780615</v>
+        <v>2781544</v>
       </c>
       <c r="E248">
         <v>2260853</v>
@@ -4587,13 +4587,13 @@
         <v>22526</v>
       </c>
       <c r="C249">
-        <v>32224</v>
+        <v>32225</v>
       </c>
       <c r="D249">
-        <v>57869</v>
+        <v>57874</v>
       </c>
       <c r="E249">
-        <v>75543</v>
+        <v>75558</v>
       </c>
     </row>
     <row r="250" spans="1:5">
@@ -4604,13 +4604,13 @@
         <v>25627716</v>
       </c>
       <c r="C250">
-        <v>29506000</v>
+        <v>29515876</v>
       </c>
       <c r="D250">
-        <v>44265839</v>
+        <v>44339891</v>
       </c>
       <c r="E250">
-        <v>71046328</v>
+        <v>71094254</v>
       </c>
     </row>
     <row r="251" spans="1:5">
@@ -4618,16 +4618,16 @@
         <v>250</v>
       </c>
       <c r="B251">
-        <v>35988366</v>
+        <v>35989033</v>
       </c>
       <c r="C251">
-        <v>44309082</v>
+        <v>44405805</v>
       </c>
       <c r="D251">
-        <v>63856352</v>
+        <v>63960698</v>
       </c>
       <c r="E251">
-        <v>90666060</v>
+        <v>90720909</v>
       </c>
     </row>
     <row r="252" spans="1:5">
@@ -4638,13 +4638,13 @@
         <v>29213387</v>
       </c>
       <c r="C252">
-        <v>35917912</v>
+        <v>35929375</v>
       </c>
       <c r="D252">
-        <v>57500159</v>
+        <v>57603597</v>
       </c>
       <c r="E252">
-        <v>96624485</v>
+        <v>96696066</v>
       </c>
     </row>
     <row r="253" spans="1:5">
@@ -4655,13 +4655,13 @@
         <v>4045637</v>
       </c>
       <c r="C253">
-        <v>5522908</v>
+        <v>5523359</v>
       </c>
       <c r="D253">
-        <v>8330088</v>
+        <v>8331609</v>
       </c>
       <c r="E253">
-        <v>12037503</v>
+        <v>12038666</v>
       </c>
     </row>
     <row r="254" spans="1:5">
@@ -4672,13 +4672,13 @@
         <v>6213487</v>
       </c>
       <c r="C254">
-        <v>7567903</v>
+        <v>7570116</v>
       </c>
       <c r="D254">
-        <v>12672778</v>
+        <v>12674436</v>
       </c>
       <c r="E254">
-        <v>26869915</v>
+        <v>26872030</v>
       </c>
     </row>
     <row r="255" spans="1:5">
@@ -4689,13 +4689,13 @@
         <v>282254</v>
       </c>
       <c r="C255">
-        <v>360190</v>
+        <v>360219</v>
       </c>
       <c r="D255">
-        <v>544959</v>
+        <v>545059</v>
       </c>
       <c r="E255">
-        <v>790785</v>
+        <v>790861</v>
       </c>
     </row>
     <row r="256" spans="1:5">
@@ -4706,13 +4706,13 @@
         <v>10602230</v>
       </c>
       <c r="C256">
-        <v>13662457</v>
+        <v>13663612</v>
       </c>
       <c r="D256">
-        <v>19493962</v>
+        <v>19498664</v>
       </c>
       <c r="E256">
-        <v>25991976</v>
+        <v>25995368</v>
       </c>
     </row>
     <row r="257" spans="1:5">
@@ -4723,13 +4723,13 @@
         <v>2051451</v>
       </c>
       <c r="C257">
-        <v>2587511</v>
+        <v>2587518</v>
       </c>
       <c r="D257">
-        <v>3410163</v>
+        <v>3410912</v>
       </c>
       <c r="E257">
-        <v>3891933</v>
+        <v>3892528</v>
       </c>
     </row>
     <row r="258" spans="1:5">
@@ -4740,13 +4740,13 @@
         <v>3674625</v>
       </c>
       <c r="C258">
-        <v>4727994</v>
+        <v>4728001</v>
       </c>
       <c r="D258">
-        <v>7273291</v>
+        <v>7273652</v>
       </c>
       <c r="E258">
-        <v>10814790</v>
+        <v>10816024</v>
       </c>
     </row>
     <row r="259" spans="1:5">
@@ -4757,13 +4757,13 @@
         <v>842101</v>
       </c>
       <c r="C259">
-        <v>855063</v>
+        <v>855064</v>
       </c>
       <c r="D259">
-        <v>1188903</v>
+        <v>1188962</v>
       </c>
       <c r="E259">
-        <v>1884395</v>
+        <v>1884610</v>
       </c>
     </row>
     <row r="260" spans="1:5">
@@ -4771,16 +4771,16 @@
         <v>259</v>
       </c>
       <c r="B260">
-        <v>10215105</v>
+        <v>10215155</v>
       </c>
       <c r="C260">
-        <v>15253167</v>
+        <v>15253452</v>
       </c>
       <c r="D260">
-        <v>26947798</v>
+        <v>26981857</v>
       </c>
       <c r="E260">
-        <v>32532474</v>
+        <v>32566740</v>
       </c>
     </row>
     <row r="261" spans="1:5">
@@ -4794,10 +4794,10 @@
         <v>437805</v>
       </c>
       <c r="D261">
-        <v>1177801</v>
+        <v>1177861</v>
       </c>
       <c r="E261">
-        <v>2682901</v>
+        <v>2683502</v>
       </c>
     </row>
     <row r="262" spans="1:5">
@@ -4808,13 +4808,13 @@
         <v>8438908</v>
       </c>
       <c r="C262">
-        <v>14980055</v>
+        <v>14980457</v>
       </c>
       <c r="D262">
-        <v>28383514</v>
+        <v>28418798</v>
       </c>
       <c r="E262">
-        <v>33416177</v>
+        <v>33451729</v>
       </c>
     </row>
     <row r="263" spans="1:5">
@@ -4825,10 +4825,10 @@
         <v>635909</v>
       </c>
       <c r="C263">
-        <v>831243</v>
+        <v>831251</v>
       </c>
       <c r="D263">
-        <v>1392851</v>
+        <v>1393147</v>
       </c>
       <c r="E263">
         <v>2255357</v>
@@ -4839,16 +4839,16 @@
         <v>263</v>
       </c>
       <c r="B264">
-        <v>1318117</v>
+        <v>1318125</v>
       </c>
       <c r="C264">
-        <v>1429205</v>
+        <v>1429212</v>
       </c>
       <c r="D264">
-        <v>2842619</v>
+        <v>2842874</v>
       </c>
       <c r="E264">
-        <v>6471599</v>
+        <v>6473342</v>
       </c>
     </row>
     <row r="265" spans="1:5">
@@ -4856,16 +4856,16 @@
         <v>264</v>
       </c>
       <c r="B265">
-        <v>694683</v>
+        <v>694688</v>
       </c>
       <c r="C265">
-        <v>816688</v>
+        <v>816693</v>
       </c>
       <c r="D265">
-        <v>1555395</v>
+        <v>1555535</v>
       </c>
       <c r="E265">
-        <v>2954426</v>
+        <v>2955221</v>
       </c>
     </row>
     <row r="266" spans="1:5">
@@ -4876,13 +4876,13 @@
         <v>3880910</v>
       </c>
       <c r="C266">
-        <v>5278872</v>
+        <v>5279132</v>
       </c>
       <c r="D266">
-        <v>10314031</v>
+        <v>10316358</v>
       </c>
       <c r="E266">
-        <v>22181512</v>
+        <v>22187896</v>
       </c>
     </row>
     <row r="267" spans="1:5">
@@ -4890,16 +4890,16 @@
         <v>266</v>
       </c>
       <c r="B267">
-        <v>854995</v>
+        <v>855000</v>
       </c>
       <c r="C267">
-        <v>1429205</v>
+        <v>1429212</v>
       </c>
       <c r="D267">
-        <v>3218059</v>
+        <v>3218347</v>
       </c>
       <c r="E267">
-        <v>6119881</v>
+        <v>6121530</v>
       </c>
     </row>
     <row r="268" spans="1:5">
@@ -4913,10 +4913,10 @@
         <v>2672916</v>
       </c>
       <c r="D268">
-        <v>5889003</v>
+        <v>5889306</v>
       </c>
       <c r="E268">
-        <v>8182848</v>
+        <v>8184680</v>
       </c>
     </row>
     <row r="269" spans="1:5">
@@ -4930,10 +4930,10 @@
         <v>5138450</v>
       </c>
       <c r="D269">
-        <v>12170606</v>
+        <v>12171232</v>
       </c>
       <c r="E269">
-        <v>19518104</v>
+        <v>19522476</v>
       </c>
     </row>
     <row r="270" spans="1:5">
@@ -4944,13 +4944,13 @@
         <v>5440842</v>
       </c>
       <c r="C270">
-        <v>11215255</v>
+        <v>11215472</v>
       </c>
       <c r="D270">
-        <v>22218592</v>
+        <v>22221468</v>
       </c>
       <c r="E270">
-        <v>28361989</v>
+        <v>28369583</v>
       </c>
     </row>
     <row r="271" spans="1:5">
@@ -4961,13 +4961,13 @@
         <v>499304</v>
       </c>
       <c r="C271">
-        <v>846043</v>
+        <v>846049</v>
       </c>
       <c r="D271">
-        <v>1963347</v>
+        <v>1963447</v>
       </c>
       <c r="E271">
-        <v>3181612</v>
+        <v>3182113</v>
       </c>
     </row>
     <row r="272" spans="1:5">
@@ -4978,13 +4978,13 @@
         <v>825380</v>
       </c>
       <c r="C272">
-        <v>1651798</v>
+        <v>1651809</v>
       </c>
       <c r="D272">
-        <v>4200650</v>
+        <v>4200864</v>
       </c>
       <c r="E272">
-        <v>7190442</v>
+        <v>7191576</v>
       </c>
     </row>
     <row r="273" spans="1:5">
@@ -4995,13 +4995,13 @@
         <v>2826186</v>
       </c>
       <c r="C273">
-        <v>6055297</v>
+        <v>6055513</v>
       </c>
       <c r="D273">
-        <v>11195832</v>
+        <v>11198190</v>
       </c>
       <c r="E273">
-        <v>12830551</v>
+        <v>12834468</v>
       </c>
     </row>
     <row r="274" spans="1:5">
@@ -5012,13 +5012,13 @@
         <v>1236456</v>
       </c>
       <c r="C274">
-        <v>2531050</v>
+        <v>2531140</v>
       </c>
       <c r="D274">
-        <v>5597916</v>
+        <v>5599095</v>
       </c>
       <c r="E274">
-        <v>9512305</v>
+        <v>9515209</v>
       </c>
     </row>
     <row r="275" spans="1:5">
@@ -5029,13 +5029,13 @@
         <v>16060910</v>
       </c>
       <c r="C275">
-        <v>25420485</v>
+        <v>25421327</v>
       </c>
       <c r="D275">
-        <v>56049776</v>
+        <v>56090875</v>
       </c>
       <c r="E275">
-        <v>70292994</v>
+        <v>70331620</v>
       </c>
     </row>
     <row r="276" spans="1:5">
@@ -5049,10 +5049,10 @@
         <v>767285</v>
       </c>
       <c r="D276">
-        <v>1986312</v>
+        <v>1986370</v>
       </c>
       <c r="E276">
-        <v>4415537</v>
+        <v>4415908</v>
       </c>
     </row>
     <row r="277" spans="1:5">
@@ -5063,13 +5063,13 @@
         <v>1943124</v>
       </c>
       <c r="C277">
-        <v>2339482</v>
+        <v>2339485</v>
       </c>
       <c r="D277">
-        <v>4647685</v>
+        <v>4648029</v>
       </c>
       <c r="E277">
-        <v>7901433</v>
+        <v>7902616</v>
       </c>
     </row>
     <row r="278" spans="1:5">
@@ -5080,13 +5080,13 @@
         <v>4936713</v>
       </c>
       <c r="C278">
-        <v>7658881</v>
+        <v>7659141</v>
       </c>
       <c r="D278">
-        <v>12996321</v>
+        <v>12997708</v>
       </c>
       <c r="E278">
-        <v>15105656</v>
+        <v>15109194</v>
       </c>
     </row>
     <row r="279" spans="1:5">
@@ -5100,10 +5100,10 @@
         <v>1551990</v>
       </c>
       <c r="D279">
-        <v>3478777</v>
+        <v>3478999</v>
       </c>
       <c r="E279">
-        <v>6422631</v>
+        <v>6423690</v>
       </c>
     </row>
     <row r="280" spans="1:5">
@@ -5117,10 +5117,10 @@
         <v>1551990</v>
       </c>
       <c r="D280">
-        <v>2889154</v>
+        <v>2889338</v>
       </c>
       <c r="E280">
-        <v>4587594</v>
+        <v>4588350</v>
       </c>
     </row>
     <row r="281" spans="1:5">
@@ -5131,13 +5131,13 @@
         <v>4018293</v>
       </c>
       <c r="C281">
-        <v>7877397</v>
+        <v>7877454</v>
       </c>
       <c r="D281">
-        <v>17818847</v>
+        <v>17819595</v>
       </c>
       <c r="E281">
-        <v>20861390</v>
+        <v>20863725</v>
       </c>
     </row>
     <row r="282" spans="1:5">
@@ -5148,13 +5148,13 @@
         <v>134193</v>
       </c>
       <c r="C282">
-        <v>299158</v>
+        <v>299166</v>
       </c>
       <c r="D282">
-        <v>830328</v>
+        <v>830356</v>
       </c>
       <c r="E282">
-        <v>1215381</v>
+        <v>1215496</v>
       </c>
     </row>
     <row r="283" spans="1:5">
@@ -5165,13 +5165,13 @@
         <v>576239</v>
       </c>
       <c r="C283">
-        <v>1111159</v>
+        <v>1111188</v>
       </c>
       <c r="D283">
-        <v>3140806</v>
+        <v>3140912</v>
       </c>
       <c r="E283">
-        <v>5524458</v>
+        <v>5524982</v>
       </c>
     </row>
     <row r="284" spans="1:5">
@@ -5182,13 +5182,13 @@
         <v>789369</v>
       </c>
       <c r="C284">
-        <v>1510036</v>
+        <v>1510076</v>
       </c>
       <c r="D284">
-        <v>3790628</v>
+        <v>3790756</v>
       </c>
       <c r="E284">
-        <v>5358724</v>
+        <v>5359233</v>
       </c>
     </row>
     <row r="285" spans="1:5">
@@ -5202,10 +5202,10 @@
         <v>1534569</v>
       </c>
       <c r="D285">
-        <v>3828165</v>
+        <v>3828276</v>
       </c>
       <c r="E285">
-        <v>6512917</v>
+        <v>6513464</v>
       </c>
     </row>
     <row r="286" spans="1:5">
@@ -5219,10 +5219,10 @@
         <v>396253</v>
       </c>
       <c r="D286">
-        <v>648586</v>
+        <v>648627</v>
       </c>
       <c r="E286">
-        <v>764599</v>
+        <v>764725</v>
       </c>
     </row>
     <row r="287" spans="1:5">
@@ -5233,10 +5233,10 @@
         <v>21913834</v>
       </c>
       <c r="C287">
-        <v>28080765</v>
+        <v>28095373</v>
       </c>
       <c r="D287">
-        <v>42661268</v>
+        <v>42676170</v>
       </c>
       <c r="E287">
         <v>62583610</v>
@@ -5250,10 +5250,10 @@
         <v>15232496</v>
       </c>
       <c r="C288">
-        <v>19866575</v>
+        <v>19877614</v>
       </c>
       <c r="D288">
-        <v>36087289</v>
+        <v>36101770</v>
       </c>
       <c r="E288">
         <v>74253701</v>
@@ -5267,13 +5267,13 @@
         <v>258549</v>
       </c>
       <c r="C289">
-        <v>271618</v>
+        <v>271708</v>
       </c>
       <c r="D289">
-        <v>438568</v>
+        <v>438658</v>
       </c>
       <c r="E289">
-        <v>851998</v>
+        <v>852093</v>
       </c>
     </row>
     <row r="290" spans="1:5">
@@ -5284,13 +5284,13 @@
         <v>5509759</v>
       </c>
       <c r="C290">
-        <v>5186261</v>
+        <v>5187772</v>
       </c>
       <c r="D290">
-        <v>9179557</v>
+        <v>9181788</v>
       </c>
       <c r="E290">
-        <v>25599508</v>
+        <v>25602907</v>
       </c>
     </row>
     <row r="291" spans="1:5">
@@ -5301,10 +5301,10 @@
         <v>6067956</v>
       </c>
       <c r="C291">
-        <v>9310927</v>
+        <v>9316749</v>
       </c>
       <c r="D291">
-        <v>18577314</v>
+        <v>18585106</v>
       </c>
       <c r="E291">
         <v>39542997</v>
@@ -5318,10 +5318,10 @@
         <v>4887481</v>
       </c>
       <c r="C292">
-        <v>6119311</v>
+        <v>6120825</v>
       </c>
       <c r="D292">
-        <v>8937049</v>
+        <v>8940428</v>
       </c>
       <c r="E292">
         <v>12350421</v>
@@ -5335,10 +5335,10 @@
         <v>14148465</v>
       </c>
       <c r="C293">
-        <v>23609330</v>
+        <v>23614964</v>
       </c>
       <c r="D293">
-        <v>35364003</v>
+        <v>35377348</v>
       </c>
       <c r="E293">
         <v>38627657</v>
@@ -5352,13 +5352,13 @@
         <v>1134452</v>
       </c>
       <c r="C294">
-        <v>1293656</v>
+        <v>1293834</v>
       </c>
       <c r="D294">
-        <v>1778273</v>
+        <v>1778722</v>
       </c>
       <c r="E294">
-        <v>2420838</v>
+        <v>2421403</v>
       </c>
     </row>
     <row r="295" spans="1:5">
@@ -5369,13 +5369,13 @@
         <v>10789503</v>
       </c>
       <c r="C295">
-        <v>16639851</v>
+        <v>16651505</v>
       </c>
       <c r="D295">
-        <v>26104032</v>
+        <v>26230078</v>
       </c>
       <c r="E295">
-        <v>26633298</v>
+        <v>26721834</v>
       </c>
     </row>
     <row r="296" spans="1:5">
@@ -5386,13 +5386,13 @@
         <v>10994710</v>
       </c>
       <c r="C296">
-        <v>16059400</v>
+        <v>16093200</v>
       </c>
       <c r="D296">
-        <v>24597471</v>
+        <v>24726376</v>
       </c>
       <c r="E296">
-        <v>26488853</v>
+        <v>26572916</v>
       </c>
     </row>
     <row r="297" spans="1:5">
@@ -5403,13 +5403,13 @@
         <v>7244025</v>
       </c>
       <c r="C297">
-        <v>9310617</v>
+        <v>9329319</v>
       </c>
       <c r="D297">
-        <v>13875342</v>
+        <v>13901054</v>
       </c>
       <c r="E297">
-        <v>16825667</v>
+        <v>16840882</v>
       </c>
     </row>
     <row r="298" spans="1:5">
@@ -5420,13 +5420,13 @@
         <v>8139265</v>
       </c>
       <c r="C298">
-        <v>11671947</v>
+        <v>11700596</v>
       </c>
       <c r="D298">
-        <v>20239056</v>
+        <v>20350627</v>
       </c>
       <c r="E298">
-        <v>27049375</v>
+        <v>27144891</v>
       </c>
     </row>
     <row r="299" spans="1:5">
@@ -5437,13 +5437,13 @@
         <v>9293347</v>
       </c>
       <c r="C299">
-        <v>12490386</v>
+        <v>12510772</v>
       </c>
       <c r="D299">
-        <v>22459293</v>
+        <v>22498904</v>
       </c>
       <c r="E299">
-        <v>36198979</v>
+        <v>36235651</v>
       </c>
     </row>
     <row r="300" spans="1:5">
@@ -5454,13 +5454,13 @@
         <v>6999716</v>
       </c>
       <c r="C300">
-        <v>10834584</v>
+        <v>10842172</v>
       </c>
       <c r="D300">
-        <v>15974109</v>
+        <v>16051242</v>
       </c>
       <c r="E300">
-        <v>14286308</v>
+        <v>14333799</v>
       </c>
     </row>
     <row r="301" spans="1:5">
@@ -5471,13 +5471,13 @@
         <v>11171581</v>
       </c>
       <c r="C301">
-        <v>15977945</v>
+        <v>15995351</v>
       </c>
       <c r="D301">
-        <v>22102044</v>
+        <v>22140635</v>
       </c>
       <c r="E301">
-        <v>20667721</v>
+        <v>20685548</v>
       </c>
     </row>
     <row r="302" spans="1:5">
@@ -5488,10 +5488,10 @@
         <v>326446</v>
       </c>
       <c r="C302">
-        <v>491533</v>
+        <v>491776</v>
       </c>
       <c r="D302">
-        <v>707738</v>
+        <v>707991</v>
       </c>
       <c r="E302">
         <v>797757</v>
@@ -5505,13 +5505,13 @@
         <v>1432322</v>
       </c>
       <c r="C303">
-        <v>1940092</v>
+        <v>1940622</v>
       </c>
       <c r="D303">
-        <v>3063307</v>
+        <v>3064049</v>
       </c>
       <c r="E303">
-        <v>4122917</v>
+        <v>4123810</v>
       </c>
     </row>
     <row r="304" spans="1:5">
@@ -5522,13 +5522,13 @@
         <v>857246</v>
       </c>
       <c r="C304">
-        <v>1663901</v>
+        <v>1664569</v>
       </c>
       <c r="D304">
-        <v>2097903</v>
+        <v>2101170</v>
       </c>
       <c r="E304">
-        <v>1042829</v>
+        <v>1043819</v>
       </c>
     </row>
     <row r="305" spans="1:5">
@@ -5539,13 +5539,13 @@
         <v>5379220</v>
       </c>
       <c r="C305">
-        <v>8602052</v>
+        <v>8605508</v>
       </c>
       <c r="D305">
-        <v>13932228</v>
+        <v>13953927</v>
       </c>
       <c r="E305">
-        <v>14808170</v>
+        <v>14822237</v>
       </c>
     </row>
     <row r="306" spans="1:5">
@@ -5556,13 +5556,13 @@
         <v>7653740</v>
       </c>
       <c r="C306">
-        <v>11336330</v>
+        <v>11337362</v>
       </c>
       <c r="D306">
-        <v>17925747</v>
+        <v>17942062</v>
       </c>
       <c r="E306">
-        <v>19161055</v>
+        <v>19174941</v>
       </c>
     </row>
     <row r="307" spans="1:5">
@@ -5573,13 +5573,13 @@
         <v>4843442</v>
       </c>
       <c r="C307">
-        <v>7848587</v>
+        <v>7851741</v>
       </c>
       <c r="D307">
-        <v>13824643</v>
+        <v>13846174</v>
       </c>
       <c r="E307">
-        <v>17102393</v>
+        <v>17118640</v>
       </c>
     </row>
     <row r="308" spans="1:5">
@@ -5590,10 +5590,10 @@
         <v>122340</v>
       </c>
       <c r="C308">
-        <v>214508</v>
+        <v>214509</v>
       </c>
       <c r="D308">
-        <v>349398</v>
+        <v>349473</v>
       </c>
       <c r="E308">
         <v>372953</v>
@@ -5607,13 +5607,13 @@
         <v>3694909</v>
       </c>
       <c r="C309">
-        <v>4931454</v>
+        <v>4931903</v>
       </c>
       <c r="D309">
-        <v>9064149</v>
+        <v>9072398</v>
       </c>
       <c r="E309">
-        <v>14586270</v>
+        <v>14596841</v>
       </c>
     </row>
     <row r="310" spans="1:5">
@@ -5624,10 +5624,10 @@
         <v>5599767</v>
       </c>
       <c r="C310">
-        <v>9001083</v>
+        <v>9002574</v>
       </c>
       <c r="D310">
-        <v>16476042</v>
+        <v>16481143</v>
       </c>
       <c r="E310">
         <v>25222655</v>
@@ -5641,13 +5641,13 @@
         <v>860863</v>
       </c>
       <c r="C311">
-        <v>1554544</v>
+        <v>1554548</v>
       </c>
       <c r="D311">
-        <v>3753490</v>
+        <v>3753679</v>
       </c>
       <c r="E311">
-        <v>5945333</v>
+        <v>5946391</v>
       </c>
     </row>
     <row r="312" spans="1:5">
@@ -5658,13 +5658,13 @@
         <v>242888</v>
       </c>
       <c r="C312">
-        <v>280146</v>
+        <v>280149</v>
       </c>
       <c r="D312">
-        <v>681781</v>
+        <v>682182</v>
       </c>
       <c r="E312">
-        <v>1694112</v>
+        <v>1698780</v>
       </c>
     </row>
     <row r="313" spans="1:5">
@@ -5675,13 +5675,13 @@
         <v>259296</v>
       </c>
       <c r="C313">
-        <v>511862</v>
+        <v>511863</v>
       </c>
       <c r="D313">
-        <v>1309357</v>
+        <v>1309423</v>
       </c>
       <c r="E313">
-        <v>2190386</v>
+        <v>2190776</v>
       </c>
     </row>
     <row r="314" spans="1:5">
@@ -5692,13 +5692,13 @@
         <v>363014</v>
       </c>
       <c r="C314">
-        <v>739356</v>
+        <v>739358</v>
       </c>
       <c r="D314">
-        <v>1571228</v>
+        <v>1571308</v>
       </c>
       <c r="E314">
-        <v>1689726</v>
+        <v>1690027</v>
       </c>
     </row>
     <row r="315" spans="1:5">
@@ -5709,13 +5709,13 @@
         <v>27691260</v>
       </c>
       <c r="C315">
-        <v>32746688</v>
+        <v>32780210</v>
       </c>
       <c r="D315">
-        <v>49567768</v>
+        <v>49651449</v>
       </c>
       <c r="E315">
-        <v>76434924</v>
+        <v>76484849</v>
       </c>
     </row>
     <row r="316" spans="1:5">
@@ -5723,16 +5723,16 @@
         <v>315</v>
       </c>
       <c r="B316">
-        <v>13603552</v>
+        <v>13604584</v>
       </c>
       <c r="C316">
-        <v>17486056</v>
+        <v>17529809</v>
       </c>
       <c r="D316">
-        <v>22986313</v>
+        <v>23080017</v>
       </c>
       <c r="E316">
-        <v>25240703</v>
+        <v>25292280</v>
       </c>
     </row>
     <row r="317" spans="1:5">
@@ -5743,13 +5743,13 @@
         <v>27688275</v>
       </c>
       <c r="C317">
-        <v>32280008</v>
+        <v>32318759</v>
       </c>
       <c r="D317">
-        <v>45948842</v>
+        <v>46108202</v>
       </c>
       <c r="E317">
-        <v>65254562</v>
+        <v>65381039</v>
       </c>
     </row>
     <row r="318" spans="1:5">
@@ -5760,13 +5760,13 @@
         <v>21376890</v>
       </c>
       <c r="C318">
-        <v>28894680</v>
+        <v>28942385</v>
       </c>
       <c r="D318">
-        <v>35134010</v>
+        <v>35280164</v>
       </c>
       <c r="E318">
-        <v>30595784</v>
+        <v>30661813</v>
       </c>
     </row>
     <row r="319" spans="1:5">
@@ -5777,13 +5777,13 @@
         <v>18181264</v>
       </c>
       <c r="C319">
-        <v>22812947</v>
+        <v>22828424</v>
       </c>
       <c r="D319">
-        <v>28951121</v>
+        <v>29076060</v>
       </c>
       <c r="E319">
-        <v>28883857</v>
+        <v>28956042</v>
       </c>
     </row>
     <row r="320" spans="1:5">
@@ -5794,13 +5794,13 @@
         <v>12834090</v>
       </c>
       <c r="C320">
-        <v>15277616</v>
+        <v>15315871</v>
       </c>
       <c r="D320">
-        <v>22797831</v>
+        <v>22909654</v>
       </c>
       <c r="E320">
-        <v>33649228</v>
+        <v>33724665</v>
       </c>
     </row>
     <row r="321" spans="1:5">
@@ -5811,13 +5811,13 @@
         <v>21257361</v>
       </c>
       <c r="C321">
-        <v>30002750</v>
+        <v>30060603</v>
       </c>
       <c r="D321">
-        <v>41634647</v>
+        <v>41812390</v>
       </c>
       <c r="E321">
-        <v>45492595</v>
+        <v>45586747</v>
       </c>
     </row>
     <row r="322" spans="1:5">
@@ -5828,13 +5828,13 @@
         <v>1505318</v>
       </c>
       <c r="C322">
-        <v>1830648</v>
+        <v>1831212</v>
       </c>
       <c r="D322">
-        <v>2669227</v>
+        <v>2669784</v>
       </c>
       <c r="E322">
-        <v>3926240</v>
+        <v>3926724</v>
       </c>
     </row>
     <row r="323" spans="1:5">
@@ -5845,13 +5845,13 @@
         <v>18430303</v>
       </c>
       <c r="C323">
-        <v>24527515</v>
+        <v>24564648</v>
       </c>
       <c r="D323">
-        <v>37939444</v>
+        <v>38113952</v>
       </c>
       <c r="E323">
-        <v>54835778</v>
+        <v>54955444</v>
       </c>
     </row>
     <row r="324" spans="1:5">
@@ -5862,13 +5862,13 @@
         <v>10404204</v>
       </c>
       <c r="C324">
-        <v>12582889</v>
+        <v>12601938</v>
       </c>
       <c r="D324">
-        <v>21360342</v>
+        <v>21458592</v>
       </c>
       <c r="E324">
-        <v>41633183</v>
+        <v>41724038</v>
       </c>
     </row>
     <row r="325" spans="1:5">
@@ -5879,13 +5879,13 @@
         <v>17538515</v>
       </c>
       <c r="C325">
-        <v>20469989</v>
+        <v>20500979</v>
       </c>
       <c r="D325">
-        <v>34213803</v>
+        <v>34371174</v>
       </c>
       <c r="E325">
-        <v>66688107</v>
+        <v>66833639</v>
       </c>
     </row>
     <row r="326" spans="1:5">
@@ -5896,13 +5896,13 @@
         <v>13999638</v>
       </c>
       <c r="C326">
-        <v>14762207</v>
+        <v>14783905</v>
       </c>
       <c r="D326">
-        <v>22729242</v>
+        <v>22815350</v>
       </c>
       <c r="E326">
-        <v>42161388</v>
+        <v>42243736</v>
       </c>
     </row>
     <row r="327" spans="1:5">
@@ -5913,10 +5913,10 @@
         <v>13823312</v>
       </c>
       <c r="C327">
-        <v>16831534</v>
+        <v>16834101</v>
       </c>
       <c r="D327">
-        <v>27714574</v>
+        <v>27723922</v>
       </c>
       <c r="E327">
         <v>52382372</v>
@@ -5930,13 +5930,13 @@
         <v>744377</v>
       </c>
       <c r="C328">
-        <v>915176</v>
+        <v>915255</v>
       </c>
       <c r="D328">
-        <v>1307203</v>
+        <v>1307500</v>
       </c>
       <c r="E328">
-        <v>1679243</v>
+        <v>1679446</v>
       </c>
     </row>
     <row r="329" spans="1:5">
@@ -5947,13 +5947,13 @@
         <v>1918445</v>
       </c>
       <c r="C329">
-        <v>2975667</v>
+        <v>2975827</v>
       </c>
       <c r="D329">
-        <v>3978858</v>
+        <v>3979777</v>
       </c>
       <c r="E329">
-        <v>3733235</v>
+        <v>3733791</v>
       </c>
     </row>
     <row r="330" spans="1:5">
@@ -5964,13 +5964,13 @@
         <v>1323337</v>
       </c>
       <c r="C330">
-        <v>1561183</v>
+        <v>1561318</v>
       </c>
       <c r="D330">
-        <v>2541784</v>
+        <v>2542361</v>
       </c>
       <c r="E330">
-        <v>4701880</v>
+        <v>4702449</v>
       </c>
     </row>
     <row r="331" spans="1:5">
@@ -5981,13 +5981,13 @@
         <v>3183869</v>
       </c>
       <c r="C331">
-        <v>3518719</v>
+        <v>3519933</v>
       </c>
       <c r="D331">
-        <v>7159127</v>
+        <v>7172154</v>
       </c>
       <c r="E331">
-        <v>23125289</v>
+        <v>23141598</v>
       </c>
     </row>
     <row r="332" spans="1:5">
@@ -5998,10 +5998,10 @@
         <v>32952530</v>
       </c>
       <c r="C332">
-        <v>36248747</v>
+        <v>36251919</v>
       </c>
       <c r="D332">
-        <v>57865910</v>
+        <v>57881530</v>
       </c>
       <c r="E332">
         <v>113091848</v>
@@ -6012,16 +6012,16 @@
         <v>332</v>
       </c>
       <c r="B333">
-        <v>16460334</v>
+        <v>16460335</v>
       </c>
       <c r="C333">
-        <v>19213684</v>
+        <v>19226965</v>
       </c>
       <c r="D333">
-        <v>31515924</v>
+        <v>31558515</v>
       </c>
       <c r="E333">
-        <v>57067548</v>
+        <v>57105086</v>
       </c>
     </row>
     <row r="334" spans="1:5">
@@ -6032,10 +6032,10 @@
         <v>16915374</v>
       </c>
       <c r="C334">
-        <v>17497169</v>
+        <v>17501352</v>
       </c>
       <c r="D334">
-        <v>25479648</v>
+        <v>25484421</v>
       </c>
       <c r="E334">
         <v>45259225</v>
@@ -6049,10 +6049,10 @@
         <v>19919886</v>
       </c>
       <c r="C335">
-        <v>23138603</v>
+        <v>23142660</v>
       </c>
       <c r="D335">
-        <v>37021217</v>
+        <v>37029277</v>
       </c>
       <c r="E335">
         <v>69821666</v>
@@ -6066,13 +6066,13 @@
         <v>1978046</v>
       </c>
       <c r="C336">
-        <v>2266856</v>
+        <v>2266872</v>
       </c>
       <c r="D336">
-        <v>4271574</v>
+        <v>4272411</v>
       </c>
       <c r="E336">
-        <v>11914934</v>
+        <v>11916308</v>
       </c>
     </row>
     <row r="337" spans="1:5">
@@ -6083,13 +6083,13 @@
         <v>7216162</v>
       </c>
       <c r="C337">
-        <v>9852206</v>
+        <v>9853259</v>
       </c>
       <c r="D337">
-        <v>17559296</v>
+        <v>17576086</v>
       </c>
       <c r="E337">
-        <v>19716741</v>
+        <v>19726765</v>
       </c>
     </row>
     <row r="338" spans="1:5">
@@ -6100,13 +6100,13 @@
         <v>5999167</v>
       </c>
       <c r="C338">
-        <v>9337275</v>
+        <v>9339304</v>
       </c>
       <c r="D338">
-        <v>14903856</v>
+        <v>14917652</v>
       </c>
       <c r="E338">
-        <v>10825821</v>
+        <v>10831350</v>
       </c>
     </row>
     <row r="339" spans="1:5">
@@ -6117,13 +6117,13 @@
         <v>10589189</v>
       </c>
       <c r="C339">
-        <v>16021792</v>
+        <v>16023503</v>
       </c>
       <c r="D339">
-        <v>31091230</v>
+        <v>31120959</v>
       </c>
       <c r="E339">
-        <v>37461808</v>
+        <v>37480854</v>
       </c>
     </row>
     <row r="340" spans="1:5">
@@ -6137,10 +6137,10 @@
         <v>302016</v>
       </c>
       <c r="D340">
-        <v>665243</v>
+        <v>665290</v>
       </c>
       <c r="E340">
-        <v>1078027</v>
+        <v>1078124</v>
       </c>
     </row>
     <row r="341" spans="1:5">
@@ -6154,7 +6154,7 @@
         <v>2151135</v>
       </c>
       <c r="D341">
-        <v>5670822</v>
+        <v>5671432</v>
       </c>
       <c r="E341">
         <v>14631455</v>
@@ -6168,13 +6168,13 @@
         <v>1277761</v>
       </c>
       <c r="C342">
-        <v>1713557</v>
+        <v>1713803</v>
       </c>
       <c r="D342">
-        <v>3958293</v>
+        <v>3958630</v>
       </c>
       <c r="E342">
-        <v>8089046</v>
+        <v>8089941</v>
       </c>
     </row>
     <row r="343" spans="1:5">
@@ -6185,13 +6185,13 @@
         <v>726306</v>
       </c>
       <c r="C343">
-        <v>886323</v>
+        <v>886450</v>
       </c>
       <c r="D343">
-        <v>1879189</v>
+        <v>1879350</v>
       </c>
       <c r="E343">
-        <v>3556886</v>
+        <v>3557279</v>
       </c>
     </row>
     <row r="344" spans="1:5">
@@ -6205,10 +6205,10 @@
         <v>469803</v>
       </c>
       <c r="D344">
-        <v>1050383</v>
+        <v>1050458</v>
       </c>
       <c r="E344">
-        <v>1745377</v>
+        <v>1745534</v>
       </c>
     </row>
     <row r="345" spans="1:5">
@@ -6222,10 +6222,10 @@
         <v>2903200</v>
       </c>
       <c r="D345">
-        <v>5987343</v>
+        <v>5987625</v>
       </c>
       <c r="E345">
-        <v>6560097</v>
+        <v>6560727</v>
       </c>
     </row>
     <row r="346" spans="1:5">
@@ -6239,10 +6239,10 @@
         <v>366169</v>
       </c>
       <c r="D346">
-        <v>992876</v>
+        <v>992923</v>
       </c>
       <c r="E346">
-        <v>1628714</v>
+        <v>1628870</v>
       </c>
     </row>
     <row r="347" spans="1:5">
@@ -6256,10 +6256,10 @@
         <v>444634</v>
       </c>
       <c r="D347">
-        <v>1053050</v>
+        <v>1053100</v>
       </c>
       <c r="E347">
-        <v>1854924</v>
+        <v>1855102</v>
       </c>
     </row>
     <row r="348" spans="1:5">
@@ -6270,13 +6270,13 @@
         <v>1858956</v>
       </c>
       <c r="C348">
-        <v>2929377</v>
+        <v>2929393</v>
       </c>
       <c r="D348">
-        <v>5188700</v>
+        <v>5189052</v>
       </c>
       <c r="E348">
-        <v>5433831</v>
+        <v>5434246</v>
       </c>
     </row>
     <row r="349" spans="1:5">
@@ -6287,13 +6287,13 @@
         <v>457362</v>
       </c>
       <c r="C349">
-        <v>574000</v>
+        <v>574003</v>
       </c>
       <c r="D349">
-        <v>1315975</v>
+        <v>1316064</v>
       </c>
       <c r="E349">
-        <v>3281819</v>
+        <v>3282069</v>
       </c>
     </row>
     <row r="350" spans="1:5">
@@ -6304,13 +6304,13 @@
         <v>929478</v>
       </c>
       <c r="C350">
-        <v>1326137</v>
+        <v>1326144</v>
       </c>
       <c r="D350">
-        <v>2744747</v>
+        <v>2744933</v>
       </c>
       <c r="E350">
-        <v>4357825</v>
+        <v>4358157</v>
       </c>
     </row>
     <row r="351" spans="1:5">
@@ -6321,13 +6321,13 @@
         <v>528110</v>
       </c>
       <c r="C351">
-        <v>1097824</v>
+        <v>1097860</v>
       </c>
       <c r="D351">
-        <v>2338237</v>
+        <v>2338318</v>
       </c>
       <c r="E351">
-        <v>2289547</v>
+        <v>2289741</v>
       </c>
     </row>
     <row r="352" spans="1:5">
@@ -6338,13 +6338,13 @@
         <v>392862</v>
       </c>
       <c r="C352">
-        <v>834804</v>
+        <v>834831</v>
       </c>
       <c r="D352">
-        <v>2310728</v>
+        <v>2310809</v>
       </c>
       <c r="E352">
-        <v>3965822</v>
+        <v>3966158</v>
       </c>
     </row>
     <row r="353" spans="1:5">
@@ -6355,10 +6355,10 @@
         <v>10728933</v>
       </c>
       <c r="C353">
-        <v>16374288</v>
+        <v>16374600</v>
       </c>
       <c r="D353">
-        <v>29926600</v>
+        <v>29929740</v>
       </c>
       <c r="E353">
         <v>36076147</v>
@@ -6372,13 +6372,13 @@
         <v>3286882</v>
       </c>
       <c r="C354">
-        <v>5961573</v>
+        <v>5961582</v>
       </c>
       <c r="D354">
-        <v>8679007</v>
+        <v>8679163</v>
       </c>
       <c r="E354">
-        <v>5186379</v>
+        <v>5186811</v>
       </c>
     </row>
     <row r="355" spans="1:5">
@@ -6389,13 +6389,13 @@
         <v>1285420</v>
       </c>
       <c r="C355">
-        <v>1970321</v>
+        <v>1970346</v>
       </c>
       <c r="D355">
-        <v>4473864</v>
+        <v>4474221</v>
       </c>
       <c r="E355">
-        <v>8289656</v>
+        <v>8290845</v>
       </c>
     </row>
     <row r="356" spans="1:5">
@@ -6406,13 +6406,13 @@
         <v>2994541</v>
       </c>
       <c r="C356">
-        <v>4150118</v>
+        <v>4150124</v>
       </c>
       <c r="D356">
-        <v>7351058</v>
+        <v>7351538</v>
       </c>
       <c r="E356">
-        <v>8837150</v>
+        <v>8837726</v>
       </c>
     </row>
     <row r="357" spans="1:5">
@@ -6423,13 +6423,13 @@
         <v>513769</v>
       </c>
       <c r="C357">
-        <v>740397</v>
+        <v>740398</v>
       </c>
       <c r="D357">
-        <v>1588420</v>
+        <v>1588523</v>
       </c>
       <c r="E357">
-        <v>2838600</v>
+        <v>2838785</v>
       </c>
     </row>
     <row r="358" spans="1:5">
@@ -6440,13 +6440,13 @@
         <v>1027539</v>
       </c>
       <c r="C358">
-        <v>1461309</v>
+        <v>1461311</v>
       </c>
       <c r="D358">
-        <v>3139899</v>
+        <v>3140104</v>
       </c>
       <c r="E358">
-        <v>5570082</v>
+        <v>5570446</v>
       </c>
     </row>
     <row r="359" spans="1:5">
@@ -6457,13 +6457,13 @@
         <v>819272</v>
       </c>
       <c r="C359">
-        <v>1839427</v>
+        <v>1839493</v>
       </c>
       <c r="D359">
-        <v>4034371</v>
+        <v>4034533</v>
       </c>
       <c r="E359">
-        <v>4012904</v>
+        <v>4013205</v>
       </c>
     </row>
     <row r="360" spans="1:5">
@@ -6474,13 +6474,13 @@
         <v>316210</v>
       </c>
       <c r="C360">
-        <v>649931</v>
+        <v>649954</v>
       </c>
       <c r="D360">
-        <v>1545078</v>
+        <v>1545140</v>
       </c>
       <c r="E360">
-        <v>1963762</v>
+        <v>1963909</v>
       </c>
     </row>
     <row r="361" spans="1:5">
@@ -6491,10 +6491,10 @@
         <v>27393218</v>
       </c>
       <c r="C361">
-        <v>44139827</v>
+        <v>44140570</v>
       </c>
       <c r="D361">
-        <v>79508169</v>
+        <v>79531389</v>
       </c>
       <c r="E361">
         <v>116085489</v>
@@ -6508,13 +6508,13 @@
         <v>162450</v>
       </c>
       <c r="C362">
-        <v>272875</v>
+        <v>272887</v>
       </c>
       <c r="D362">
-        <v>530428</v>
+        <v>530545</v>
       </c>
       <c r="E362">
-        <v>733049</v>
+        <v>733250</v>
       </c>
     </row>
     <row r="363" spans="1:5">
@@ -6528,10 +6528,10 @@
         <v>3318844</v>
       </c>
       <c r="D363">
-        <v>6648587</v>
+        <v>6649244</v>
       </c>
       <c r="E363">
-        <v>10723157</v>
+        <v>10724834</v>
       </c>
     </row>
     <row r="364" spans="1:5">
@@ -6542,13 +6542,13 @@
         <v>11184589</v>
       </c>
       <c r="C364">
-        <v>17885023</v>
+        <v>17889137</v>
       </c>
       <c r="D364">
-        <v>31821793</v>
+        <v>31831521</v>
       </c>
       <c r="E364">
-        <v>45234571</v>
+        <v>45247019</v>
       </c>
     </row>
     <row r="365" spans="1:5">
@@ -6559,13 +6559,13 @@
         <v>407148</v>
       </c>
       <c r="C365">
-        <v>196108</v>
+        <v>196153</v>
       </c>
       <c r="D365">
-        <v>461185</v>
+        <v>461326</v>
       </c>
       <c r="E365">
-        <v>4141765</v>
+        <v>4142905</v>
       </c>
     </row>
     <row r="366" spans="1:5">
@@ -6576,13 +6576,13 @@
         <v>239658</v>
       </c>
       <c r="C366">
-        <v>395894</v>
+        <v>395961</v>
       </c>
       <c r="D366">
-        <v>786484</v>
+        <v>786806</v>
       </c>
       <c r="E366">
-        <v>1237474</v>
+        <v>1237853</v>
       </c>
     </row>
     <row r="367" spans="1:5">
@@ -6590,16 +6590,16 @@
         <v>366</v>
       </c>
       <c r="B367">
-        <v>516186</v>
+        <v>516187</v>
       </c>
       <c r="C367">
-        <v>857770</v>
+        <v>857916</v>
       </c>
       <c r="D367">
-        <v>1754465</v>
+        <v>1755183</v>
       </c>
       <c r="E367">
-        <v>2939002</v>
+        <v>2939902</v>
       </c>
     </row>
     <row r="368" spans="1:5">
@@ -6610,13 +6610,13 @@
         <v>847693</v>
       </c>
       <c r="C368">
-        <v>1381405</v>
+        <v>1381626</v>
       </c>
       <c r="D368">
-        <v>3176242</v>
+        <v>3177439</v>
       </c>
       <c r="E368">
-        <v>7080210</v>
+        <v>7082376</v>
       </c>
     </row>
     <row r="369" spans="1:5">
@@ -6627,13 +6627,13 @@
         <v>147482</v>
       </c>
       <c r="C369">
-        <v>230938</v>
+        <v>230977</v>
       </c>
       <c r="D369">
-        <v>544489</v>
+        <v>544712</v>
       </c>
       <c r="E369">
-        <v>1160132</v>
+        <v>1160487</v>
       </c>
     </row>
     <row r="370" spans="1:5">
@@ -6644,13 +6644,13 @@
         <v>1722394</v>
       </c>
       <c r="C370">
-        <v>3226309</v>
+        <v>3226421</v>
       </c>
       <c r="D370">
-        <v>7222110</v>
+        <v>7223062</v>
       </c>
       <c r="E370">
-        <v>11820716</v>
+        <v>11824045</v>
       </c>
     </row>
     <row r="371" spans="1:5">
@@ -6661,13 +6661,13 @@
         <v>256224</v>
       </c>
       <c r="C371">
-        <v>352454</v>
+        <v>352466</v>
       </c>
       <c r="D371">
-        <v>777766</v>
+        <v>777868</v>
       </c>
       <c r="E371">
-        <v>1625348</v>
+        <v>1625806</v>
       </c>
     </row>
     <row r="372" spans="1:5">
@@ -6678,13 +6678,13 @@
         <v>1167242</v>
       </c>
       <c r="C372">
-        <v>2602737</v>
+        <v>2602827</v>
       </c>
       <c r="D372">
-        <v>6722118</v>
+        <v>6723004</v>
       </c>
       <c r="E372">
-        <v>12855029</v>
+        <v>12858649</v>
       </c>
     </row>
     <row r="373" spans="1:5">
@@ -6695,10 +6695,10 @@
         <v>16676366</v>
       </c>
       <c r="C373">
-        <v>26950191</v>
+        <v>26950235</v>
       </c>
       <c r="D373">
-        <v>44837763</v>
+        <v>44843993</v>
       </c>
       <c r="E373">
         <v>48507915</v>
@@ -6712,10 +6712,10 @@
         <v>8951307</v>
       </c>
       <c r="C374">
-        <v>14231072</v>
+        <v>14231081</v>
       </c>
       <c r="D374">
-        <v>24003307</v>
+        <v>24006000</v>
       </c>
       <c r="E374">
         <v>22360590</v>
@@ -6729,13 +6729,13 @@
         <v>421860</v>
       </c>
       <c r="C375">
-        <v>889507</v>
+        <v>889508</v>
       </c>
       <c r="D375">
-        <v>1649305</v>
+        <v>1649459</v>
       </c>
       <c r="E375">
-        <v>1659928</v>
+        <v>1660302</v>
       </c>
     </row>
     <row r="376" spans="1:5">
@@ -6746,13 +6746,13 @@
         <v>742643</v>
       </c>
       <c r="C376">
-        <v>915015</v>
+        <v>915058</v>
       </c>
       <c r="D376">
-        <v>2056331</v>
+        <v>2056489</v>
       </c>
       <c r="E376">
-        <v>4604559</v>
+        <v>4605298</v>
       </c>
     </row>
     <row r="377" spans="1:5">
@@ -6763,13 +6763,13 @@
         <v>2440114</v>
       </c>
       <c r="C377">
-        <v>3685477</v>
+        <v>3685649</v>
       </c>
       <c r="D377">
-        <v>8029483</v>
+        <v>8030099</v>
       </c>
       <c r="E377">
-        <v>13546747</v>
+        <v>13548921</v>
       </c>
     </row>
     <row r="378" spans="1:5">
@@ -6780,10 +6780,10 @@
         <v>17472691</v>
       </c>
       <c r="C378">
-        <v>26954657</v>
+        <v>26955374</v>
       </c>
       <c r="D378">
-        <v>43714914</v>
+        <v>43721947</v>
       </c>
       <c r="E378">
         <v>51486257</v>
@@ -6797,10 +6797,10 @@
         <v>225616</v>
       </c>
       <c r="C379">
-        <v>369242</v>
+        <v>369252</v>
       </c>
       <c r="D379">
-        <v>603797</v>
+        <v>603894</v>
       </c>
       <c r="E379">
         <v>682439</v>
@@ -6814,13 +6814,13 @@
         <v>79315</v>
       </c>
       <c r="C380">
-        <v>116380</v>
+        <v>116382</v>
       </c>
       <c r="D380">
-        <v>187747</v>
+        <v>187768</v>
       </c>
       <c r="E380">
-        <v>230477</v>
+        <v>230538</v>
       </c>
     </row>
     <row r="381" spans="1:5">
@@ -6831,13 +6831,13 @@
         <v>555202</v>
       </c>
       <c r="C381">
-        <v>814660</v>
+        <v>814672</v>
       </c>
       <c r="D381">
-        <v>1251647</v>
+        <v>1251785</v>
       </c>
       <c r="E381">
-        <v>1306036</v>
+        <v>1306381</v>
       </c>
     </row>
     <row r="382" spans="1:5">
@@ -6848,13 +6848,13 @@
         <v>954466</v>
       </c>
       <c r="C382">
-        <v>1573191</v>
+        <v>1573224</v>
       </c>
       <c r="D382">
-        <v>2725834</v>
+        <v>2726204</v>
       </c>
       <c r="E382">
-        <v>3097915</v>
+        <v>3098683</v>
       </c>
     </row>
     <row r="383" spans="1:5">
@@ -6865,13 +6865,13 @@
         <v>13966884</v>
       </c>
       <c r="C383">
-        <v>21681089</v>
+        <v>21681234</v>
       </c>
       <c r="D383">
-        <v>33403432</v>
+        <v>33409712</v>
       </c>
       <c r="E383">
-        <v>37888185</v>
+        <v>37898343</v>
       </c>
     </row>
     <row r="384" spans="1:5">
@@ -6885,10 +6885,10 @@
         <v>104726</v>
       </c>
       <c r="D384">
-        <v>178450</v>
+        <v>178474</v>
       </c>
       <c r="E384">
-        <v>223878</v>
+        <v>223935</v>
       </c>
     </row>
     <row r="385" spans="1:5">
@@ -6899,13 +6899,13 @@
         <v>3434266</v>
       </c>
       <c r="C385">
-        <v>3626897</v>
+        <v>3627239</v>
       </c>
       <c r="D385">
-        <v>5531676</v>
+        <v>5533105</v>
       </c>
       <c r="E385">
-        <v>9604119</v>
+        <v>9606321</v>
       </c>
     </row>
     <row r="386" spans="1:5">
@@ -6916,13 +6916,13 @@
         <v>2814044</v>
       </c>
       <c r="C386">
-        <v>4826091</v>
+        <v>4826096</v>
       </c>
       <c r="D386">
-        <v>8347412</v>
+        <v>8348287</v>
       </c>
       <c r="E386">
-        <v>8923279</v>
+        <v>8925011</v>
       </c>
     </row>
     <row r="387" spans="1:5">
@@ -6933,13 +6933,13 @@
         <v>1931207</v>
       </c>
       <c r="C387">
-        <v>3413576</v>
+        <v>3413580</v>
       </c>
       <c r="D387">
-        <v>6983456</v>
+        <v>6984188</v>
       </c>
       <c r="E387">
-        <v>10136845</v>
+        <v>10138813</v>
       </c>
     </row>
     <row r="388" spans="1:5">
@@ -6950,10 +6950,10 @@
         <v>6800469</v>
       </c>
       <c r="C388">
-        <v>12191050</v>
+        <v>12191132</v>
       </c>
       <c r="D388">
-        <v>31991773</v>
+        <v>31992248</v>
       </c>
       <c r="E388">
         <v>38441900</v>
@@ -6967,13 +6967,13 @@
         <v>294920</v>
       </c>
       <c r="C389">
-        <v>497071</v>
+        <v>497072</v>
       </c>
       <c r="D389">
-        <v>1604982</v>
+        <v>1604993</v>
       </c>
       <c r="E389">
-        <v>2797589</v>
+        <v>2797702</v>
       </c>
     </row>
     <row r="390" spans="1:5">
@@ -6984,13 +6984,13 @@
         <v>264826</v>
       </c>
       <c r="C390">
-        <v>467831</v>
+        <v>467832</v>
       </c>
       <c r="D390">
-        <v>1483851</v>
+        <v>1483862</v>
       </c>
       <c r="E390">
-        <v>2339802</v>
+        <v>2339896</v>
       </c>
     </row>
     <row r="391" spans="1:5">
@@ -7001,10 +7001,10 @@
         <v>545128</v>
       </c>
       <c r="C391">
-        <v>886040</v>
+        <v>886046</v>
       </c>
       <c r="D391">
-        <v>2913920</v>
+        <v>2913963</v>
       </c>
       <c r="E391">
         <v>6077771</v>
@@ -7018,13 +7018,13 @@
         <v>168526</v>
       </c>
       <c r="C392">
-        <v>282648</v>
+        <v>282649</v>
       </c>
       <c r="D392">
-        <v>1059894</v>
+        <v>1059901</v>
       </c>
       <c r="E392">
-        <v>2594128</v>
+        <v>2594233</v>
       </c>
     </row>
     <row r="393" spans="1:5">
@@ -7035,13 +7035,13 @@
         <v>895552</v>
       </c>
       <c r="C393">
-        <v>1444187</v>
+        <v>1444188</v>
       </c>
       <c r="D393">
-        <v>4456751</v>
+        <v>4456783</v>
       </c>
       <c r="E393">
-        <v>7555588</v>
+        <v>7555722</v>
       </c>
     </row>
     <row r="394" spans="1:5">
@@ -7055,10 +7055,10 @@
         <v>382060</v>
       </c>
       <c r="D394">
-        <v>1312140</v>
+        <v>1312149</v>
       </c>
       <c r="E394">
-        <v>3037422</v>
+        <v>3037476</v>
       </c>
     </row>
     <row r="395" spans="1:5">
@@ -7069,13 +7069,13 @@
         <v>1051061</v>
       </c>
       <c r="C395">
-        <v>1666238</v>
+        <v>1666239</v>
       </c>
       <c r="D395">
-        <v>4919327</v>
+        <v>4919372</v>
       </c>
       <c r="E395">
-        <v>8421385</v>
+        <v>8421590</v>
       </c>
     </row>
     <row r="396" spans="1:5">
@@ -7089,10 +7089,10 @@
         <v>466547</v>
       </c>
       <c r="D396">
-        <v>1365172</v>
+        <v>1365185</v>
       </c>
       <c r="E396">
-        <v>2522535</v>
+        <v>2522596</v>
       </c>
     </row>
     <row r="397" spans="1:5">
@@ -7106,10 +7106,10 @@
         <v>860203</v>
       </c>
       <c r="D397">
-        <v>2545372</v>
+        <v>2545381</v>
       </c>
       <c r="E397">
-        <v>3972843</v>
+        <v>3972968</v>
       </c>
     </row>
     <row r="398" spans="1:5">
@@ -7123,10 +7123,10 @@
         <v>270626</v>
       </c>
       <c r="D398">
-        <v>795429</v>
+        <v>795432</v>
       </c>
       <c r="E398">
-        <v>1381858</v>
+        <v>1381902</v>
       </c>
     </row>
     <row r="399" spans="1:5">
@@ -7140,7 +7140,7 @@
         <v>10470223</v>
       </c>
       <c r="D399">
-        <v>35260050</v>
+        <v>35261045</v>
       </c>
       <c r="E399">
         <v>50120142</v>
@@ -7157,10 +7157,10 @@
         <v>544757</v>
       </c>
       <c r="D400">
-        <v>2128439</v>
+        <v>2128492</v>
       </c>
       <c r="E400">
-        <v>3620693</v>
+        <v>3621046</v>
       </c>
     </row>
     <row r="401" spans="1:5">
@@ -7174,10 +7174,10 @@
         <v>468032</v>
       </c>
       <c r="D401">
-        <v>1718212</v>
+        <v>1718255</v>
       </c>
       <c r="E401">
-        <v>3799006</v>
+        <v>3799390</v>
       </c>
     </row>
     <row r="402" spans="1:5">
@@ -7191,10 +7191,10 @@
         <v>344123</v>
       </c>
       <c r="D402">
-        <v>1396375</v>
+        <v>1396391</v>
       </c>
       <c r="E402">
-        <v>3571542</v>
+        <v>3571819</v>
       </c>
     </row>
     <row r="403" spans="1:5">
@@ -7208,10 +7208,10 @@
         <v>898850</v>
       </c>
       <c r="D403">
-        <v>3957567</v>
+        <v>3957666</v>
       </c>
       <c r="E403">
-        <v>10026535</v>
+        <v>10027511</v>
       </c>
     </row>
     <row r="404" spans="1:5">
@@ -7225,10 +7225,10 @@
         <v>2350658</v>
       </c>
       <c r="D404">
-        <v>7796574</v>
+        <v>7796699</v>
       </c>
       <c r="E404">
-        <v>8688382</v>
+        <v>8688950</v>
       </c>
     </row>
     <row r="405" spans="1:5">
@@ -7242,10 +7242,10 @@
         <v>152829</v>
       </c>
       <c r="D405">
-        <v>525612</v>
+        <v>525620</v>
       </c>
       <c r="E405">
-        <v>609711</v>
+        <v>609751</v>
       </c>
     </row>
     <row r="406" spans="1:5">
@@ -7259,10 +7259,10 @@
         <v>123719</v>
       </c>
       <c r="D406">
-        <v>408809</v>
+        <v>408816</v>
       </c>
       <c r="E406">
-        <v>457283</v>
+        <v>457313</v>
       </c>
     </row>
     <row r="407" spans="1:5">
@@ -7276,10 +7276,10 @@
         <v>1324671</v>
       </c>
       <c r="D407">
-        <v>5191568</v>
+        <v>5191617</v>
       </c>
       <c r="E407">
-        <v>7293373</v>
+        <v>7293741</v>
       </c>
     </row>
     <row r="408" spans="1:5">
@@ -7296,7 +7296,7 @@
         <v>26488</v>
       </c>
       <c r="E408">
-        <v>47360</v>
+        <v>47362</v>
       </c>
     </row>
     <row r="409" spans="1:5">
@@ -7310,10 +7310,10 @@
         <v>18313</v>
       </c>
       <c r="D409">
-        <v>79463</v>
+        <v>79464</v>
       </c>
       <c r="E409">
-        <v>94719</v>
+        <v>94724</v>
       </c>
     </row>
     <row r="410" spans="1:5">
@@ -7321,13 +7321,13 @@
         <v>409</v>
       </c>
       <c r="B410">
-        <v>6660244</v>
+        <v>6660288</v>
       </c>
       <c r="C410">
-        <v>15623578</v>
+        <v>15625746</v>
       </c>
       <c r="D410">
-        <v>34991465</v>
+        <v>35001947</v>
       </c>
       <c r="E410">
         <v>45615394</v>
@@ -7341,13 +7341,13 @@
         <v>164086</v>
       </c>
       <c r="C411">
-        <v>241270</v>
+        <v>241276</v>
       </c>
       <c r="D411">
-        <v>791574</v>
+        <v>791689</v>
       </c>
       <c r="E411">
-        <v>3592800</v>
+        <v>3593700</v>
       </c>
     </row>
     <row r="412" spans="1:5">
@@ -7358,13 +7358,13 @@
         <v>27348</v>
       </c>
       <c r="C412">
-        <v>60317</v>
+        <v>60319</v>
       </c>
       <c r="D412">
-        <v>148420</v>
+        <v>148442</v>
       </c>
       <c r="E412">
-        <v>211341</v>
+        <v>211394</v>
       </c>
     </row>
     <row r="413" spans="1:5">
@@ -7375,13 +7375,13 @@
         <v>213925</v>
       </c>
       <c r="C413">
-        <v>370132</v>
+        <v>370141</v>
       </c>
       <c r="D413">
-        <v>1153388</v>
+        <v>1153550</v>
       </c>
       <c r="E413">
-        <v>3562117</v>
+        <v>3562965</v>
       </c>
     </row>
     <row r="414" spans="1:5">
@@ -7389,16 +7389,16 @@
         <v>413</v>
       </c>
       <c r="B414">
-        <v>189824</v>
+        <v>189825</v>
       </c>
       <c r="C414">
-        <v>416492</v>
+        <v>416523</v>
       </c>
       <c r="D414">
-        <v>942199</v>
+        <v>942456</v>
       </c>
       <c r="E414">
-        <v>1343586</v>
+        <v>1343988</v>
       </c>
     </row>
     <row r="415" spans="1:5">
@@ -7409,13 +7409,13 @@
         <v>2309819</v>
       </c>
       <c r="C415">
-        <v>4968870</v>
+        <v>4969007</v>
       </c>
       <c r="D415">
-        <v>12416778</v>
+        <v>12419022</v>
       </c>
       <c r="E415">
-        <v>19385278</v>
+        <v>19390407</v>
       </c>
     </row>
     <row r="416" spans="1:5">
@@ -7426,13 +7426,13 @@
         <v>119991</v>
       </c>
       <c r="C416">
-        <v>257011</v>
+        <v>257018</v>
       </c>
       <c r="D416">
-        <v>608169</v>
+        <v>608279</v>
       </c>
       <c r="E416">
-        <v>997772</v>
+        <v>998036</v>
       </c>
     </row>
     <row r="417" spans="1:5">
@@ -7443,13 +7443,13 @@
         <v>706521</v>
       </c>
       <c r="C417">
-        <v>1628170</v>
+        <v>1628195</v>
       </c>
       <c r="D417">
-        <v>4446917</v>
+        <v>4447248</v>
       </c>
       <c r="E417">
-        <v>5879040</v>
+        <v>5880112</v>
       </c>
     </row>
     <row r="418" spans="1:5">
@@ -7463,10 +7463,10 @@
         <v>14668</v>
       </c>
       <c r="D418">
-        <v>41560</v>
+        <v>41563</v>
       </c>
       <c r="E418">
-        <v>63215</v>
+        <v>63227</v>
       </c>
     </row>
     <row r="419" spans="1:5">
@@ -7480,7 +7480,7 @@
         <v>1219390</v>
       </c>
       <c r="D419">
-        <v>2696342</v>
+        <v>2696510</v>
       </c>
       <c r="E419">
         <v>3741666</v>
@@ -7497,7 +7497,7 @@
         <v>362006</v>
       </c>
       <c r="D420">
-        <v>826298</v>
+        <v>826350</v>
       </c>
       <c r="E420">
         <v>1268361</v>
@@ -7514,10 +7514,10 @@
         <v>2458090</v>
       </c>
       <c r="D421">
-        <v>5030877</v>
+        <v>5033862</v>
       </c>
       <c r="E421">
-        <v>5307168</v>
+        <v>5310433</v>
       </c>
     </row>
     <row r="422" spans="1:5">
@@ -7531,10 +7531,10 @@
         <v>934979</v>
       </c>
       <c r="D422">
-        <v>2263895</v>
+        <v>2265238</v>
       </c>
       <c r="E422">
-        <v>3086822</v>
+        <v>3088721</v>
       </c>
     </row>
     <row r="423" spans="1:5">
@@ -7548,7 +7548,7 @@
         <v>2286355</v>
       </c>
       <c r="D423">
-        <v>4566385</v>
+        <v>4566669</v>
       </c>
       <c r="E423">
         <v>4946610</v>
@@ -7565,7 +7565,7 @@
         <v>2743626</v>
       </c>
       <c r="D424">
-        <v>5436173</v>
+        <v>5436511</v>
       </c>
       <c r="E424">
         <v>5073446</v>
@@ -7582,10 +7582,10 @@
         <v>452409</v>
       </c>
       <c r="D425">
-        <v>826501</v>
+        <v>826992</v>
       </c>
       <c r="E425">
-        <v>487393</v>
+        <v>487693</v>
       </c>
     </row>
     <row r="426" spans="1:5">
@@ -7599,7 +7599,7 @@
         <v>533483</v>
       </c>
       <c r="D426">
-        <v>1043745</v>
+        <v>1043810</v>
       </c>
       <c r="E426">
         <v>1648870</v>
@@ -7616,10 +7616,10 @@
         <v>604560</v>
       </c>
       <c r="D427">
-        <v>1449380</v>
+        <v>1449440</v>
       </c>
       <c r="E427">
-        <v>3093740</v>
+        <v>3094164</v>
       </c>
     </row>
     <row r="428" spans="1:5">
@@ -7633,10 +7633,10 @@
         <v>2075655</v>
       </c>
       <c r="D428">
-        <v>4801070</v>
+        <v>4801268</v>
       </c>
       <c r="E428">
-        <v>6574198</v>
+        <v>6575099</v>
       </c>
     </row>
     <row r="429" spans="1:5">
@@ -7650,7 +7650,7 @@
         <v>457271</v>
       </c>
       <c r="D429">
-        <v>1348171</v>
+        <v>1348255</v>
       </c>
       <c r="E429">
         <v>4756355</v>
@@ -7667,7 +7667,7 @@
         <v>990754</v>
       </c>
       <c r="D430">
-        <v>2130980</v>
+        <v>2131112</v>
       </c>
       <c r="E430">
         <v>2473305</v>
@@ -7684,10 +7684,10 @@
         <v>2427929</v>
       </c>
       <c r="D431">
-        <v>5354291</v>
+        <v>5357467</v>
       </c>
       <c r="E431">
-        <v>6390264</v>
+        <v>6394195</v>
       </c>
     </row>
     <row r="432" spans="1:5">
@@ -7701,7 +7701,7 @@
         <v>2953209</v>
       </c>
       <c r="D432">
-        <v>6479918</v>
+        <v>6480321</v>
       </c>
       <c r="E432">
         <v>7546750</v>
@@ -7718,7 +7718,7 @@
         <v>609695</v>
       </c>
       <c r="D433">
-        <v>1565618</v>
+        <v>1565715</v>
       </c>
       <c r="E433">
         <v>3487994</v>
@@ -7735,7 +7735,7 @@
         <v>487241</v>
       </c>
       <c r="D434">
-        <v>1423334</v>
+        <v>1423389</v>
       </c>
       <c r="E434">
         <v>1946126</v>
@@ -7752,7 +7752,7 @@
         <v>457271</v>
       </c>
       <c r="D435">
-        <v>1043745</v>
+        <v>1043810</v>
       </c>
       <c r="E435">
         <v>1331779</v>
@@ -7769,10 +7769,10 @@
         <v>1029710</v>
       </c>
       <c r="D436">
-        <v>2556246</v>
+        <v>2556294</v>
       </c>
       <c r="E436">
-        <v>3812264</v>
+        <v>3812634</v>
       </c>
     </row>
     <row r="437" spans="1:5">
@@ -7786,10 +7786,10 @@
         <v>881250</v>
       </c>
       <c r="D437">
-        <v>2546405</v>
+        <v>2546433</v>
       </c>
       <c r="E437">
-        <v>3798429</v>
+        <v>3798581</v>
       </c>
     </row>
     <row r="438" spans="1:5">
@@ -7803,10 +7803,10 @@
         <v>819768</v>
       </c>
       <c r="D438">
-        <v>2060013</v>
+        <v>2060036</v>
       </c>
       <c r="E438">
-        <v>1967861</v>
+        <v>1967939</v>
       </c>
     </row>
     <row r="439" spans="1:5">
@@ -7820,10 +7820,10 @@
         <v>276672</v>
       </c>
       <c r="D439">
-        <v>886950</v>
+        <v>886960</v>
       </c>
       <c r="E439">
-        <v>1967861</v>
+        <v>1967939</v>
       </c>
     </row>
     <row r="440" spans="1:5">
@@ -7837,10 +7837,10 @@
         <v>727544</v>
       </c>
       <c r="D440">
-        <v>1688066</v>
+        <v>1688085</v>
       </c>
       <c r="E440">
-        <v>1555983</v>
+        <v>1556045</v>
       </c>
     </row>
     <row r="441" spans="1:5">
@@ -7854,10 +7854,10 @@
         <v>225436</v>
       </c>
       <c r="D441">
-        <v>572226</v>
+        <v>572232</v>
       </c>
       <c r="E441">
-        <v>777991</v>
+        <v>778023</v>
       </c>
     </row>
     <row r="442" spans="1:5">
@@ -7871,10 +7871,10 @@
         <v>236664</v>
       </c>
       <c r="D442">
-        <v>641261</v>
+        <v>641284</v>
       </c>
       <c r="E442">
-        <v>1019970</v>
+        <v>1020129</v>
       </c>
     </row>
     <row r="443" spans="1:5">
@@ -7888,10 +7888,10 @@
         <v>276672</v>
       </c>
       <c r="D443">
-        <v>686671</v>
+        <v>686679</v>
       </c>
       <c r="E443">
-        <v>777991</v>
+        <v>778023</v>
       </c>
     </row>
     <row r="444" spans="1:5">
@@ -7905,10 +7905,10 @@
         <v>348401</v>
       </c>
       <c r="D444">
-        <v>801116</v>
+        <v>801125</v>
       </c>
       <c r="E444">
-        <v>777991</v>
+        <v>778023</v>
       </c>
     </row>
     <row r="445" spans="1:5">
@@ -7922,10 +7922,10 @@
         <v>10247</v>
       </c>
       <c r="D445">
-        <v>28611</v>
+        <v>28612</v>
       </c>
       <c r="E445">
-        <v>45764</v>
+        <v>45766</v>
       </c>
     </row>
     <row r="446" spans="1:5">
@@ -7939,10 +7939,10 @@
         <v>153706</v>
       </c>
       <c r="D446">
-        <v>400558</v>
+        <v>400563</v>
       </c>
       <c r="E446">
-        <v>732227</v>
+        <v>732257</v>
       </c>
     </row>
     <row r="447" spans="1:5">
@@ -7956,10 +7956,10 @@
         <v>10247</v>
       </c>
       <c r="D447">
-        <v>28611</v>
+        <v>28612</v>
       </c>
       <c r="E447">
-        <v>45764</v>
+        <v>45766</v>
       </c>
     </row>
     <row r="448" spans="1:5">
@@ -7973,10 +7973,10 @@
         <v>228642</v>
       </c>
       <c r="D448">
-        <v>424679</v>
+        <v>424685</v>
       </c>
       <c r="E448">
-        <v>775518</v>
+        <v>775590</v>
       </c>
     </row>
     <row r="449" spans="1:5">
@@ -7990,10 +7990,10 @@
         <v>1771974</v>
       </c>
       <c r="D449">
-        <v>3078920</v>
+        <v>3078966</v>
       </c>
       <c r="E449">
-        <v>3384078</v>
+        <v>3384391</v>
       </c>
     </row>
     <row r="450" spans="1:5">
@@ -8007,10 +8007,10 @@
         <v>685925</v>
       </c>
       <c r="D450">
-        <v>1220951</v>
+        <v>1220969</v>
       </c>
       <c r="E450">
-        <v>1903544</v>
+        <v>1903720</v>
       </c>
     </row>
     <row r="451" spans="1:5">
@@ -8024,10 +8024,10 @@
         <v>1457591</v>
       </c>
       <c r="D451">
-        <v>3132005</v>
+        <v>3132052</v>
       </c>
       <c r="E451">
-        <v>5428625</v>
+        <v>5429128</v>
       </c>
     </row>
     <row r="452" spans="1:5">
@@ -8041,10 +8041,10 @@
         <v>1314690</v>
       </c>
       <c r="D452">
-        <v>2707327</v>
+        <v>2707367</v>
       </c>
       <c r="E452">
-        <v>4864612</v>
+        <v>4865063</v>
       </c>
     </row>
     <row r="453" spans="1:5">
@@ -8058,10 +8058,10 @@
         <v>1086048</v>
       </c>
       <c r="D453">
-        <v>2707327</v>
+        <v>2707367</v>
       </c>
       <c r="E453">
-        <v>7050163</v>
+        <v>7050815</v>
       </c>
     </row>
     <row r="454" spans="1:5">
@@ -8072,13 +8072,13 @@
         <v>759777</v>
       </c>
       <c r="C454">
-        <v>1127898</v>
+        <v>1127901</v>
       </c>
       <c r="D454">
-        <v>2291243</v>
+        <v>2291316</v>
       </c>
       <c r="E454">
-        <v>3377158</v>
+        <v>3377531</v>
       </c>
     </row>
     <row r="455" spans="1:5">
@@ -8089,13 +8089,13 @@
         <v>379888</v>
       </c>
       <c r="C455">
-        <v>506403</v>
+        <v>506405</v>
       </c>
       <c r="D455">
-        <v>1169997</v>
+        <v>1170034</v>
       </c>
       <c r="E455">
-        <v>2161381</v>
+        <v>2161620</v>
       </c>
     </row>
     <row r="456" spans="1:5">
@@ -8106,13 +8106,13 @@
         <v>436168</v>
       </c>
       <c r="C456">
-        <v>690550</v>
+        <v>690552</v>
       </c>
       <c r="D456">
-        <v>1657495</v>
+        <v>1657548</v>
       </c>
       <c r="E456">
-        <v>3106986</v>
+        <v>3107329</v>
       </c>
     </row>
     <row r="457" spans="1:5">
@@ -8126,10 +8126,10 @@
         <v>184147</v>
       </c>
       <c r="D457">
-        <v>438749</v>
+        <v>438763</v>
       </c>
       <c r="E457">
-        <v>540345</v>
+        <v>540405</v>
       </c>
     </row>
     <row r="458" spans="1:5">
@@ -8140,13 +8140,13 @@
         <v>548728</v>
       </c>
       <c r="C458">
-        <v>1196953</v>
+        <v>1196957</v>
       </c>
       <c r="D458">
-        <v>2437493</v>
+        <v>2437570</v>
       </c>
       <c r="E458">
-        <v>2431554</v>
+        <v>2431822</v>
       </c>
     </row>
     <row r="459" spans="1:5">
@@ -8157,13 +8157,13 @@
         <v>239189</v>
       </c>
       <c r="C459">
-        <v>414330</v>
+        <v>414331</v>
       </c>
       <c r="D459">
-        <v>926247</v>
+        <v>926277</v>
       </c>
       <c r="E459">
-        <v>1283320</v>
+        <v>1283462</v>
       </c>
     </row>
     <row r="460" spans="1:5">
@@ -8174,13 +8174,13 @@
         <v>562797</v>
       </c>
       <c r="C460">
-        <v>1104880</v>
+        <v>1104883</v>
       </c>
       <c r="D460">
-        <v>1998744</v>
+        <v>1998807</v>
       </c>
       <c r="E460">
-        <v>1688579</v>
+        <v>1688766</v>
       </c>
     </row>
     <row r="461" spans="1:5">
@@ -8191,13 +8191,13 @@
         <v>576867</v>
       </c>
       <c r="C461">
-        <v>1058843</v>
+        <v>1058846</v>
       </c>
       <c r="D461">
-        <v>2291243</v>
+        <v>2291316</v>
       </c>
       <c r="E461">
-        <v>2971899</v>
+        <v>2972227</v>
       </c>
     </row>
     <row r="462" spans="1:5">
@@ -8211,10 +8211,10 @@
         <v>184147</v>
       </c>
       <c r="D462">
-        <v>389999</v>
+        <v>390011</v>
       </c>
       <c r="E462">
-        <v>540345</v>
+        <v>540405</v>
       </c>
     </row>
     <row r="463" spans="1:5">
@@ -8228,10 +8228,10 @@
         <v>1330032</v>
       </c>
       <c r="D463">
-        <v>2853466</v>
+        <v>2853584</v>
       </c>
       <c r="E463">
-        <v>3609364</v>
+        <v>3609859</v>
       </c>
     </row>
     <row r="464" spans="1:5">
@@ -8245,10 +8245,10 @@
         <v>1209120</v>
       </c>
       <c r="D464">
-        <v>2762880</v>
+        <v>2762994</v>
       </c>
       <c r="E464">
-        <v>3416005</v>
+        <v>3416473</v>
       </c>
     </row>
     <row r="465" spans="1:5">
@@ -8262,7 +8262,7 @@
         <v>67672</v>
       </c>
       <c r="D465">
-        <v>173577</v>
+        <v>173584</v>
       </c>
       <c r="E465">
         <v>216236</v>
@@ -8279,10 +8279,10 @@
         <v>455724</v>
       </c>
       <c r="D466">
-        <v>1409366</v>
+        <v>1409402</v>
       </c>
       <c r="E466">
-        <v>1705927</v>
+        <v>1706056</v>
       </c>
     </row>
     <row r="467" spans="1:5">
@@ -8296,10 +8296,10 @@
         <v>544104</v>
       </c>
       <c r="D467">
-        <v>1268207</v>
+        <v>1268260</v>
       </c>
       <c r="E467">
-        <v>1482417</v>
+        <v>1482620</v>
       </c>
     </row>
     <row r="468" spans="1:5">
@@ -8313,10 +8313,10 @@
         <v>600185</v>
       </c>
       <c r="D468">
-        <v>1327121</v>
+        <v>1327140</v>
       </c>
       <c r="E468">
-        <v>3807088</v>
+        <v>3807440</v>
       </c>
     </row>
     <row r="469" spans="1:5">
@@ -8330,10 +8330,10 @@
         <v>514444</v>
       </c>
       <c r="D469">
-        <v>1114782</v>
+        <v>1114798</v>
       </c>
       <c r="E469">
-        <v>2679062</v>
+        <v>2679310</v>
       </c>
     </row>
     <row r="470" spans="1:5">
@@ -8347,10 +8347,10 @@
         <v>885987</v>
       </c>
       <c r="D470">
-        <v>1751800</v>
+        <v>1751825</v>
       </c>
       <c r="E470">
-        <v>3595583</v>
+        <v>3595916</v>
       </c>
     </row>
     <row r="471" spans="1:5">
@@ -8364,10 +8364,10 @@
         <v>201520</v>
       </c>
       <c r="D471">
-        <v>498224</v>
+        <v>498245</v>
       </c>
       <c r="E471">
-        <v>837888</v>
+        <v>838003</v>
       </c>
     </row>
     <row r="472" spans="1:5">
@@ -8378,13 +8378,13 @@
         <v>154769</v>
       </c>
       <c r="C472">
-        <v>230183</v>
+        <v>230184</v>
       </c>
       <c r="D472">
-        <v>536248</v>
+        <v>536265</v>
       </c>
       <c r="E472">
-        <v>878061</v>
+        <v>878158</v>
       </c>
     </row>
     <row r="473" spans="1:5">
@@ -8398,10 +8398,10 @@
         <v>284827</v>
       </c>
       <c r="D473">
-        <v>758889</v>
+        <v>758909</v>
       </c>
       <c r="E473">
-        <v>1210658</v>
+        <v>1210749</v>
       </c>
     </row>
     <row r="474" spans="1:5">
@@ -8415,10 +8415,10 @@
         <v>740551</v>
       </c>
       <c r="D474">
-        <v>1951430</v>
+        <v>1951480</v>
       </c>
       <c r="E474">
-        <v>2861554</v>
+        <v>2861772</v>
       </c>
     </row>
     <row r="475" spans="1:5">
@@ -8432,10 +8432,10 @@
         <v>652633</v>
       </c>
       <c r="D475">
-        <v>1704164</v>
+        <v>1704196</v>
       </c>
       <c r="E475">
-        <v>2803135</v>
+        <v>2803407</v>
       </c>
     </row>
     <row r="476" spans="1:5">
@@ -8449,10 +8449,10 @@
         <v>974536</v>
       </c>
       <c r="D476">
-        <v>2619429</v>
+        <v>2619508</v>
       </c>
       <c r="E476">
-        <v>3902784</v>
+        <v>3903112</v>
       </c>
     </row>
     <row r="477" spans="1:5">
@@ -8466,10 +8466,10 @@
         <v>280346</v>
       </c>
       <c r="D477">
-        <v>861182</v>
+        <v>861208</v>
       </c>
       <c r="E477">
-        <v>1209313</v>
+        <v>1209415</v>
       </c>
     </row>
     <row r="478" spans="1:5">
@@ -8480,13 +8480,13 @@
         <v>1206303</v>
       </c>
       <c r="C478">
-        <v>2225381</v>
+        <v>2225710</v>
       </c>
       <c r="D478">
-        <v>5292012</v>
+        <v>5293856</v>
       </c>
       <c r="E478">
-        <v>5511057</v>
+        <v>5513883</v>
       </c>
     </row>
     <row r="479" spans="1:5">
@@ -8497,13 +8497,13 @@
         <v>179539</v>
       </c>
       <c r="C479">
-        <v>325328</v>
+        <v>325329</v>
       </c>
       <c r="D479">
-        <v>825494</v>
+        <v>825511</v>
       </c>
       <c r="E479">
-        <v>1037686</v>
+        <v>1037778</v>
       </c>
     </row>
     <row r="480" spans="1:5">
@@ -8514,10 +8514,10 @@
         <v>150302</v>
       </c>
       <c r="C480">
-        <v>268747</v>
+        <v>268750</v>
       </c>
       <c r="D480">
-        <v>761175</v>
+        <v>761201</v>
       </c>
       <c r="E480">
         <v>1459717</v>
@@ -8531,13 +8531,13 @@
         <v>2896826</v>
       </c>
       <c r="C481">
-        <v>5205129</v>
+        <v>5205897</v>
       </c>
       <c r="D481">
-        <v>11668723</v>
+        <v>11672787</v>
       </c>
       <c r="E481">
-        <v>10970609</v>
+        <v>10976234</v>
       </c>
     </row>
     <row r="482" spans="1:5">
@@ -8548,13 +8548,13 @@
         <v>1087372</v>
       </c>
       <c r="C482">
-        <v>1810480</v>
+        <v>1810747</v>
       </c>
       <c r="D482">
-        <v>4798968</v>
+        <v>4800639</v>
       </c>
       <c r="E482">
-        <v>6850192</v>
+        <v>6853705</v>
       </c>
     </row>
     <row r="483" spans="1:5">
@@ -8565,13 +8565,13 @@
         <v>2038822</v>
       </c>
       <c r="C483">
-        <v>3118048</v>
+        <v>3118508</v>
       </c>
       <c r="D483">
-        <v>7592887</v>
+        <v>7595532</v>
       </c>
       <c r="E483">
-        <v>9992010</v>
+        <v>9997134</v>
       </c>
     </row>
     <row r="484" spans="1:5">
@@ -8582,13 +8582,13 @@
         <v>2599498</v>
       </c>
       <c r="C484">
-        <v>4224452</v>
+        <v>4225076</v>
       </c>
       <c r="D484">
-        <v>10781242</v>
+        <v>10784998</v>
       </c>
       <c r="E484">
-        <v>14730489</v>
+        <v>14738042</v>
       </c>
     </row>
     <row r="485" spans="1:5">
@@ -8599,10 +8599,10 @@
         <v>403938</v>
       </c>
       <c r="C485">
-        <v>569111</v>
+        <v>569118</v>
       </c>
       <c r="D485">
-        <v>1722658</v>
+        <v>1722717</v>
       </c>
       <c r="E485">
         <v>4379151</v>
@@ -8616,10 +8616,10 @@
         <v>965670</v>
       </c>
       <c r="C486">
-        <v>1855091</v>
+        <v>1855095</v>
       </c>
       <c r="D486">
-        <v>4687545</v>
+        <v>4687703</v>
       </c>
       <c r="E486">
         <v>6098204</v>
@@ -8636,10 +8636,10 @@
         <v>1183123</v>
       </c>
       <c r="D487">
-        <v>3129886</v>
+        <v>3129922</v>
       </c>
       <c r="E487">
-        <v>5269741</v>
+        <v>5270145</v>
       </c>
     </row>
     <row r="488" spans="1:5">
@@ -8650,13 +8650,13 @@
         <v>1088160</v>
       </c>
       <c r="C488">
-        <v>1924174</v>
+        <v>1924184</v>
       </c>
       <c r="D488">
-        <v>5349475</v>
+        <v>5349558</v>
       </c>
       <c r="E488">
-        <v>8828895</v>
+        <v>8829515</v>
       </c>
     </row>
     <row r="489" spans="1:5">
@@ -8667,13 +8667,13 @@
         <v>193656</v>
       </c>
       <c r="C489">
-        <v>204079</v>
+        <v>204080</v>
       </c>
       <c r="D489">
-        <v>516501</v>
+        <v>516509</v>
       </c>
       <c r="E489">
-        <v>1012230</v>
+        <v>1012301</v>
       </c>
     </row>
     <row r="490" spans="1:5">
@@ -8684,10 +8684,10 @@
         <v>1242183</v>
       </c>
       <c r="C490">
-        <v>2667060</v>
+        <v>2667103</v>
       </c>
       <c r="D490">
-        <v>5094649</v>
+        <v>5095196</v>
       </c>
       <c r="E490">
         <v>4764107</v>
@@ -8701,13 +8701,13 @@
         <v>98004</v>
       </c>
       <c r="C491">
-        <v>174919</v>
+        <v>174920</v>
       </c>
       <c r="D491">
-        <v>367026</v>
+        <v>367059</v>
       </c>
       <c r="E491">
-        <v>426267</v>
+        <v>426360</v>
       </c>
     </row>
     <row r="492" spans="1:5">
@@ -8718,10 +8718,10 @@
         <v>3409396</v>
       </c>
       <c r="C492">
-        <v>7293112</v>
+        <v>7293228</v>
       </c>
       <c r="D492">
-        <v>14476874</v>
+        <v>14478429</v>
       </c>
       <c r="E492">
         <v>14642622</v>
@@ -8735,10 +8735,10 @@
         <v>1374330</v>
       </c>
       <c r="C493">
-        <v>2383833</v>
+        <v>2383871</v>
       </c>
       <c r="D493">
-        <v>5750396</v>
+        <v>5751013</v>
       </c>
       <c r="E493">
         <v>10438998</v>
@@ -8752,10 +8752,10 @@
         <v>3488684</v>
       </c>
       <c r="C494">
-        <v>6325418</v>
+        <v>6325518</v>
       </c>
       <c r="D494">
-        <v>12862728</v>
+        <v>12864109</v>
       </c>
       <c r="E494">
         <v>15973769</v>
@@ -8769,13 +8769,13 @@
         <v>14109</v>
       </c>
       <c r="C495">
-        <v>26649</v>
+        <v>26650</v>
       </c>
       <c r="D495">
-        <v>54708</v>
+        <v>54717</v>
       </c>
       <c r="E495">
-        <v>72895</v>
+        <v>72913</v>
       </c>
     </row>
     <row r="496" spans="1:5">
@@ -8786,13 +8786,13 @@
         <v>16132</v>
       </c>
       <c r="C496">
-        <v>29448</v>
+        <v>29449</v>
       </c>
       <c r="D496">
-        <v>57100</v>
+        <v>57109</v>
       </c>
       <c r="E496">
-        <v>74553</v>
+        <v>74572</v>
       </c>
     </row>
     <row r="497" spans="1:5">
@@ -8803,13 +8803,13 @@
         <v>888848</v>
       </c>
       <c r="C497">
-        <v>1572309</v>
+        <v>1572360</v>
       </c>
       <c r="D497">
-        <v>3173092</v>
+        <v>3173560</v>
       </c>
       <c r="E497">
-        <v>4373702</v>
+        <v>4374776</v>
       </c>
     </row>
     <row r="498" spans="1:5">
@@ -8820,13 +8820,13 @@
         <v>4026790</v>
       </c>
       <c r="C498">
-        <v>7531429</v>
+        <v>7531463</v>
       </c>
       <c r="D498">
-        <v>14509337</v>
+        <v>14510579</v>
       </c>
       <c r="E498">
-        <v>16950283</v>
+        <v>16954216</v>
       </c>
     </row>
     <row r="499" spans="1:5">
@@ -8837,13 +8837,13 @@
         <v>623394</v>
       </c>
       <c r="C499">
-        <v>1040707</v>
+        <v>1040711</v>
       </c>
       <c r="D499">
-        <v>2207943</v>
+        <v>2208132</v>
       </c>
       <c r="E499">
-        <v>3557467</v>
+        <v>3558292</v>
       </c>
     </row>
     <row r="500" spans="1:5">
@@ -8854,13 +8854,13 @@
         <v>286424</v>
       </c>
       <c r="C500">
-        <v>547740</v>
+        <v>547743</v>
       </c>
       <c r="D500">
-        <v>1051401</v>
+        <v>1051491</v>
       </c>
       <c r="E500">
-        <v>1325331</v>
+        <v>1325638</v>
       </c>
     </row>
     <row r="501" spans="1:5">
@@ -8874,10 +8874,10 @@
         <v>2277815</v>
       </c>
       <c r="D501">
-        <v>5796605</v>
+        <v>5796724</v>
       </c>
       <c r="E501">
-        <v>9252520</v>
+        <v>9253213</v>
       </c>
     </row>
   </sheetData>
